--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_9_41.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_9_41.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4688372.911188489</v>
+        <v>4728323.352143592</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6764066.245458337</v>
+        <v>6764066.245458387</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6764066.245458337</v>
+        <v>6764066.245458387</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3307259.142253664</v>
+        <v>3307259.142253737</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3307259.142253664</v>
+        <v>3307259.142253737</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>47231338.16997886</v>
+        <v>47231338.16997884</v>
       </c>
     </row>
   </sheetData>
@@ -666,10 +666,10 @@
         <v>404.3632896068686</v>
       </c>
       <c r="F2" t="n">
-        <v>404.8896287080119</v>
+        <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>100.2478051614518</v>
+        <v>3.75737228701621</v>
       </c>
       <c r="H2" t="n">
         <v>408.0096587035274</v>
@@ -678,13 +678,13 @@
         <v>150.0811596826846</v>
       </c>
       <c r="J2" t="n">
-        <v>798.7814999999999</v>
+        <v>419.7382696589336</v>
       </c>
       <c r="K2" t="n">
-        <v>798.7814999999998</v>
+        <v>815</v>
       </c>
       <c r="L2" t="n">
-        <v>731.9356864956435</v>
+        <v>667.9495278946607</v>
       </c>
       <c r="M2" t="n">
         <v>298.9910820919849</v>
@@ -699,16 +699,16 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>371.9706110579117</v>
+        <v>798.7814999999999</v>
       </c>
       <c r="R2" t="n">
         <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
-        <v>94.84816780232291</v>
+        <v>191.3386006767583</v>
       </c>
       <c r="T2" t="n">
-        <v>186.6755817285639</v>
+        <v>586.6755817285639</v>
       </c>
       <c r="U2" t="n">
         <v>249.2212965486107</v>
@@ -742,13 +742,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -787,10 +787,10 @@
         <v>66.5639999646113</v>
       </c>
       <c r="T3" t="n">
-        <v>350.36788217258</v>
+        <v>5.357765217513816</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2103597601867477</v>
+        <v>16.44508595618974</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
@@ -900,28 +900,28 @@
         <v>10.33915573984979</v>
       </c>
       <c r="E5" t="n">
-        <v>4.363289606868648</v>
+        <v>404.3632896068686</v>
       </c>
       <c r="F5" t="n">
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>3.75737228701621</v>
+        <v>403.7573722870162</v>
       </c>
       <c r="H5" t="n">
         <v>408.0096587035274</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J5" t="n">
         <v>419.7382696589336</v>
       </c>
       <c r="K5" t="n">
-        <v>98.12488247690067</v>
+        <v>279.7604168367467</v>
       </c>
       <c r="L5" t="n">
-        <v>783.0093003026393</v>
+        <v>815</v>
       </c>
       <c r="M5" t="n">
         <v>298.9910820919849</v>
@@ -933,22 +933,22 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>601.8153451151105</v>
+        <v>815</v>
       </c>
       <c r="Q5" t="n">
-        <v>798.7814999999999</v>
+        <v>371.9706110579117</v>
       </c>
       <c r="R5" t="n">
-        <v>97.4501913854146</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S5" t="n">
-        <v>494.8481678023229</v>
+        <v>191.3386006767583</v>
       </c>
       <c r="T5" t="n">
-        <v>586.6755817285639</v>
+        <v>186.6755817285639</v>
       </c>
       <c r="U5" t="n">
-        <v>649.2212965486107</v>
+        <v>249.2212965486107</v>
       </c>
       <c r="V5" t="n">
         <v>229.8510241668239</v>
@@ -970,13 +970,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>73.16906773709609</v>
+        <v>57.7256243834227</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
         <v>414.5106671915202</v>
       </c>
       <c r="W6" t="n">
-        <v>32.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X6" t="n">
         <v>19.86273944538755</v>
@@ -1134,19 +1134,19 @@
         <v>49.47457824299391</v>
       </c>
       <c r="D8" t="n">
-        <v>410.3391557398498</v>
+        <v>10.33915573984979</v>
       </c>
       <c r="E8" t="n">
         <v>4.363289606868648</v>
       </c>
       <c r="F8" t="n">
-        <v>404.8896287080119</v>
+        <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>3.75737228701621</v>
+        <v>403.7573722870162</v>
       </c>
       <c r="H8" t="n">
-        <v>408.0096587035274</v>
+        <v>8.009658703527407</v>
       </c>
       <c r="I8" t="n">
         <v>150.0811596826846</v>
@@ -1155,7 +1155,7 @@
         <v>419.7382696589336</v>
       </c>
       <c r="K8" t="n">
-        <v>98.12488247690067</v>
+        <v>578.7514989287423</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1167,25 +1167,25 @@
         <v>195.5855355810472</v>
       </c>
       <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
         <v>815</v>
-      </c>
-      <c r="P8" t="n">
-        <v>480.626616451896</v>
       </c>
       <c r="Q8" t="n">
         <v>371.9706110579117</v>
       </c>
       <c r="R8" t="n">
-        <v>250.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>94.84816780232291</v>
+        <v>494.8481678023229</v>
       </c>
       <c r="T8" t="n">
-        <v>186.6755817285639</v>
+        <v>586.6755817285639</v>
       </c>
       <c r="U8" t="n">
-        <v>249.2212965486107</v>
+        <v>596.5903282513405</v>
       </c>
       <c r="V8" t="n">
         <v>229.8510241668239</v>
@@ -1197,7 +1197,7 @@
         <v>192.2818334606677</v>
       </c>
       <c r="Y8" t="n">
-        <v>207.8078655572417</v>
+        <v>111.3174326828064</v>
       </c>
     </row>
     <row r="9">
@@ -1213,16 +1213,16 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>118.6979892794115</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>19.27058108003868</v>
       </c>
       <c r="F9" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R9" t="n">
         <v>147.2737972923793</v>
@@ -1276,7 +1276,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
-        <v>399.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1368,7 +1368,7 @@
         <v>256.9993129555745</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>224.4745782429939</v>
       </c>
       <c r="D11" t="n">
         <v>185.3391557398498</v>
@@ -1383,7 +1383,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>167.0661201055379</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1413,10 +1413,10 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>25.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>269.8481678023229</v>
+        <v>55.30864978963361</v>
       </c>
       <c r="T11" t="n">
         <v>361.6755817285639</v>
@@ -1526,22 +1526,22 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>47.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>14.08036958171074</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>49.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1550,7 +1550,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>63.52077380114304</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>169.8386795915058</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>340.7767994885276</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1623,7 +1623,7 @@
         <v>129.0096587035274</v>
       </c>
       <c r="I14" t="n">
-        <v>3.450191385413969</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1650,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3.450191385414405</v>
       </c>
       <c r="S14" t="n">
         <v>215.8481678023229</v>
@@ -1760,16 +1760,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8.113800337078658</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>6.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>1.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>144.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -1799,13 +1799,13 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>208.1490942168662</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>408.4478973282775</v>
+        <v>339.4016293563778</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>446.839266425598</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -1829,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>8.465352849462363</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1851,7 +1851,7 @@
         <v>125.3632896068686</v>
       </c>
       <c r="F17" t="n">
-        <v>125.8896287080119</v>
+        <v>129.3398200934258</v>
       </c>
       <c r="G17" t="n">
         <v>124.7573722870162</v>
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>219.2983591877372</v>
+        <v>215.8481678023229</v>
       </c>
       <c r="T17" t="n">
         <v>307.6755817285639</v>
@@ -2003,7 +2003,7 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -2033,16 +2033,16 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>292.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>39.9174744735842</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>338.6387678008247</v>
       </c>
       <c r="R19" t="n">
         <v>447.6021279811511</v>
@@ -2270,22 +2270,22 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>292.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.234443479157942</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
         <v>408.4478973282775</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>377.7929984536983</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>83.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2331,7 +2331,7 @@
         <v>124.7573722870162</v>
       </c>
       <c r="H23" t="n">
-        <v>129.0096587035274</v>
+        <v>132.4598500889414</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.450191385414405</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>215.8481678023229</v>
@@ -2477,10 +2477,10 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>6.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>1.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2498,7 +2498,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>9.520773801143037</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>408.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>338.6387678008247</v>
       </c>
       <c r="R25" t="n">
-        <v>359.7551017600433</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2553,22 +2553,22 @@
         <v>256.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>224.4745782429939</v>
+        <v>212.696475845388</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>179.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>183.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2610,13 +2610,13 @@
         <v>424.2212965486107</v>
       </c>
       <c r="V26" t="n">
-        <v>39.33480592446158</v>
+        <v>404.8510241668239</v>
       </c>
       <c r="W26" t="n">
         <v>413.3734759809475</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>367.2818334606677</v>
       </c>
       <c r="Y26" t="n">
         <v>286.3174326828064</v>
@@ -2726,7 +2726,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -2750,13 +2750,13 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>345.9207354288559</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>340.7767994885276</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2771,7 +2771,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -2787,22 +2787,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>230.9993129555745</v>
       </c>
       <c r="C29" t="n">
-        <v>198.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>159.3391557398498</v>
       </c>
       <c r="E29" t="n">
-        <v>153.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>153.8896287080119</v>
+        <v>130.2262602303051</v>
       </c>
       <c r="G29" t="n">
-        <v>152.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>157.0096587035274</v>
@@ -2847,7 +2847,7 @@
         <v>398.2212965486107</v>
       </c>
       <c r="V29" t="n">
-        <v>341.9091611906191</v>
+        <v>378.8510241668239</v>
       </c>
       <c r="W29" t="n">
         <v>387.3734759809475</v>
@@ -2856,7 +2856,7 @@
         <v>341.2818334606677</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>260.3174326828064</v>
       </c>
     </row>
     <row r="30">
@@ -2981,13 +2981,13 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>52.97841917455702</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>52.97841917455702</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -3030,7 +3030,7 @@
         <v>161.4745782429939</v>
       </c>
       <c r="D32" t="n">
-        <v>112.0805471252643</v>
+        <v>122.3391557398498</v>
       </c>
       <c r="E32" t="n">
         <v>116.3632896068686</v>
@@ -3051,7 +3051,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>47.83862152371714</v>
+        <v>47.83862152371154</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>206.8481678023229</v>
+        <v>196.5895591877376</v>
       </c>
       <c r="T32" t="n">
         <v>298.6755817285639</v>
@@ -3212,13 +3212,13 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>25.69528484364604</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>232.6316114025499</v>
       </c>
       <c r="N34" t="n">
-        <v>29.2992253894274</v>
+        <v>283.1850752716849</v>
       </c>
       <c r="O34" t="n">
         <v>352.445564079015</v>
@@ -3227,13 +3227,13 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>437.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>74.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3291,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>47.83862152368385</v>
+        <v>47.83862152371714</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>196.5895591877376</v>
+        <v>206.8481678023229</v>
       </c>
       <c r="T35" t="n">
         <v>298.6755817285639</v>
@@ -3321,7 +3321,7 @@
         <v>361.2212965486107</v>
       </c>
       <c r="V35" t="n">
-        <v>341.8510241668239</v>
+        <v>331.5924155522381</v>
       </c>
       <c r="W35" t="n">
         <v>350.3734759809475</v>
@@ -3452,22 +3452,22 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>142.0640741896034</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>352.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
         <v>399.4478973282775</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>437.839266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>56.67037184302035</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3525,10 +3525,10 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>47.83862153580866</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>47.83862152370594</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -3549,10 +3549,10 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>206.8481678023229</v>
+        <v>196.5895591877376</v>
       </c>
       <c r="T38" t="n">
-        <v>288.4169731143282</v>
+        <v>298.6755817285639</v>
       </c>
       <c r="U38" t="n">
         <v>361.2212965486107</v>
@@ -3686,28 +3686,28 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>135.5476281577792</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>232.6316114025499</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>283.1850752716849</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>242.5932207648817</v>
       </c>
       <c r="P40" t="n">
-        <v>399.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>437.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>56.67037184302035</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3735,25 +3735,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>229.6957888009625</v>
       </c>
       <c r="C41" t="n">
-        <v>254.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>215.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>209.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>209.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>208.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>213.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3783,16 +3783,16 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>55.87859882829446</v>
       </c>
       <c r="S41" t="n">
         <v>299.8481678023229</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>391.6755817285639</v>
       </c>
       <c r="U41" t="n">
-        <v>217.9194160788313</v>
+        <v>454.2212965486107</v>
       </c>
       <c r="V41" t="n">
         <v>434.8510241668239</v>
@@ -3801,7 +3801,7 @@
         <v>443.3734759809475</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>397.2818334606677</v>
       </c>
       <c r="Y41" t="n">
         <v>316.3174326828064</v>
@@ -3826,13 +3826,13 @@
         <v>147.6720972219126</v>
       </c>
       <c r="F42" t="n">
-        <v>144.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>130.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>137.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>22.12638589134853</v>
@@ -3862,10 +3862,10 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>154.0207569166868</v>
+        <v>352.2737972923793</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>271.5639999646113</v>
       </c>
       <c r="T42" t="n">
         <v>210.3577652175138</v>
@@ -3877,10 +3877,10 @@
         <v>219.5106671915202</v>
       </c>
       <c r="W42" t="n">
-        <v>237.3731429098285</v>
+        <v>6.302119502620316</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>224.8627394453875</v>
       </c>
       <c r="Y42" t="n">
         <v>204.3913927661343</v>
@@ -3908,7 +3908,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>50.04387284153003</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
         <v>33.77112610161862</v>
@@ -3941,19 +3941,19 @@
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>59.36564461079053</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>15.02456650625771</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>4.170310216216194</v>
       </c>
       <c r="W43" t="n">
         <v>31.37280983870968</v>
@@ -3975,25 +3975,25 @@
         <v>366.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>245.2100886922616</v>
       </c>
       <c r="D44" t="n">
-        <v>295.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>289.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>35.76220549479871</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>288.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>293.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>35.08115968268461</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4020,25 +4020,25 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>135.8785988282945</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>379.8481678023229</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>471.6755817285639</v>
       </c>
       <c r="U44" t="n">
-        <v>534.2212965486107</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>514.8510241668239</v>
       </c>
       <c r="W44" t="n">
-        <v>523.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>477.2818334606677</v>
       </c>
       <c r="Y44" t="n">
         <v>396.3174326828064</v>
@@ -4057,13 +4057,13 @@
         <v>246.0999124455193</v>
       </c>
       <c r="D45" t="n">
-        <v>232.9376868977026</v>
+        <v>69.84677101847318</v>
       </c>
       <c r="E45" t="n">
-        <v>227.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>224.6362423378769</v>
       </c>
       <c r="G45" t="n">
         <v>210.7395358750273</v>
@@ -4072,7 +4072,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>102.1263858913485</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>58.07926509047959</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -4105,22 +4105,22 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>290.3577652175138</v>
       </c>
       <c r="U45" t="n">
         <v>285.2103597601867</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>299.5106671915202</v>
       </c>
       <c r="W45" t="n">
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>275.6770451606312</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>284.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -4184,10 +4184,10 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>78.1444032459268</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>35.95839127445794</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -4297,19 +4297,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1608.033611965038</v>
+        <v>1106.528124213083</v>
       </c>
       <c r="C2" t="n">
-        <v>1558.059290507469</v>
+        <v>1056.553802755514</v>
       </c>
       <c r="D2" t="n">
-        <v>1547.615698851055</v>
+        <v>1046.1102110991</v>
       </c>
       <c r="E2" t="n">
-        <v>1139.16793157139</v>
+        <v>637.6624438194344</v>
       </c>
       <c r="F2" t="n">
-        <v>730.1885086340038</v>
+        <v>632.7234249224528</v>
       </c>
       <c r="G2" t="n">
         <v>628.9280993800121</v>
@@ -4321,25 +4321,25 @@
         <v>65.2</v>
       </c>
       <c r="J2" t="n">
-        <v>65.2</v>
+        <v>448.0719498394611</v>
       </c>
       <c r="K2" t="n">
-        <v>65.2</v>
+        <v>431.6896266071377</v>
       </c>
       <c r="L2" t="n">
-        <v>101.0502310413578</v>
+        <v>532.1723410838711</v>
       </c>
       <c r="M2" t="n">
-        <v>605.8890370090498</v>
+        <v>1037.011147051563</v>
       </c>
       <c r="N2" t="n">
-        <v>1215.177889957487</v>
+        <v>1646.3</v>
       </c>
       <c r="O2" t="n">
-        <v>2022.027889957487</v>
+        <v>2453.15</v>
       </c>
       <c r="P2" t="n">
-        <v>2828.877889957487</v>
+        <v>3260</v>
       </c>
       <c r="Q2" t="n">
         <v>3260</v>
@@ -4348,25 +4348,25 @@
         <v>3006.587273910814</v>
       </c>
       <c r="S2" t="n">
-        <v>2910.781043807457</v>
+        <v>2813.315960095906</v>
       </c>
       <c r="T2" t="n">
-        <v>2722.219850142241</v>
+        <v>2220.714362390286</v>
       </c>
       <c r="U2" t="n">
-        <v>2470.481166759806</v>
+        <v>1968.975679007851</v>
       </c>
       <c r="V2" t="n">
-        <v>2238.308415076146</v>
+        <v>1736.80292732419</v>
       </c>
       <c r="W2" t="n">
-        <v>1997.527126206502</v>
+        <v>1496.021638454547</v>
       </c>
       <c r="X2" t="n">
-        <v>1803.303052003807</v>
+        <v>1301.797564251852</v>
       </c>
       <c r="Y2" t="n">
-        <v>1690.861200809053</v>
+        <v>1189.355713057098</v>
       </c>
     </row>
     <row r="3">
@@ -4376,19 +4376,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>408.2669114524009</v>
+        <v>740.3632657544849</v>
       </c>
       <c r="C3" t="n">
-        <v>408.2669114524009</v>
+        <v>740.3632657544849</v>
       </c>
       <c r="D3" t="n">
-        <v>408.2669114524009</v>
+        <v>740.3632657544849</v>
       </c>
       <c r="E3" t="n">
-        <v>408.2669114524009</v>
+        <v>394.2298342171994</v>
       </c>
       <c r="F3" t="n">
-        <v>65.2</v>
+        <v>394.2298342171994</v>
       </c>
       <c r="G3" t="n">
         <v>65.2</v>
@@ -4430,22 +4430,22 @@
         <v>829.8071048660403</v>
       </c>
       <c r="T3" t="n">
-        <v>475.9001531765655</v>
+        <v>824.3952208079455</v>
       </c>
       <c r="U3" t="n">
-        <v>475.6876685703162</v>
+        <v>807.7840228724003</v>
       </c>
       <c r="V3" t="n">
-        <v>461.0304289829222</v>
+        <v>793.1267832850062</v>
       </c>
       <c r="W3" t="n">
-        <v>428.33028462956</v>
+        <v>760.4266389316441</v>
       </c>
       <c r="X3" t="n">
-        <v>408.2669114524009</v>
+        <v>740.3632657544849</v>
       </c>
       <c r="Y3" t="n">
-        <v>408.2669114524009</v>
+        <v>740.3632657544849</v>
       </c>
     </row>
     <row r="4">
@@ -4455,31 +4455,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>752.1354558294097</v>
+        <v>176.9573376662921</v>
       </c>
       <c r="C4" t="n">
-        <v>878.1374616478455</v>
+        <v>302.9593434847279</v>
       </c>
       <c r="D4" t="n">
-        <v>943.6880323260742</v>
+        <v>416.278487609728</v>
       </c>
       <c r="E4" t="n">
-        <v>1061.516936537487</v>
+        <v>534.1073918211411</v>
       </c>
       <c r="F4" t="n">
-        <v>1061.516936537487</v>
+        <v>560.5030385051385</v>
       </c>
       <c r="G4" t="n">
-        <v>1214.923502424373</v>
+        <v>713.9096043920238</v>
       </c>
       <c r="H4" t="n">
-        <v>1214.923502424373</v>
+        <v>883.4261895514213</v>
       </c>
       <c r="I4" t="n">
-        <v>1214.923502424373</v>
+        <v>1104.559068487504</v>
       </c>
       <c r="J4" t="n">
-        <v>1576.007243076824</v>
+        <v>1465.642809139955</v>
       </c>
       <c r="K4" t="n">
         <v>1576.007243076824</v>
@@ -4506,25 +4506,25 @@
         <v>65.2</v>
       </c>
       <c r="S4" t="n">
-        <v>102.4502550941731</v>
+        <v>65.2</v>
       </c>
       <c r="T4" t="n">
-        <v>290.525934252978</v>
+        <v>65.2</v>
       </c>
       <c r="U4" t="n">
-        <v>290.525934252978</v>
+        <v>65.2</v>
       </c>
       <c r="V4" t="n">
-        <v>489.347327138924</v>
+        <v>65.2</v>
       </c>
       <c r="W4" t="n">
-        <v>489.347327138924</v>
+        <v>65.2</v>
       </c>
       <c r="X4" t="n">
-        <v>640.3781181631175</v>
+        <v>65.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>640.3781181631175</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="5">
@@ -4534,25 +4534,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>550.8905891800684</v>
+        <v>1510.568528253487</v>
       </c>
       <c r="C5" t="n">
-        <v>500.9162677224988</v>
+        <v>1460.594206795918</v>
       </c>
       <c r="D5" t="n">
-        <v>490.4726760660849</v>
+        <v>1450.150615139504</v>
       </c>
       <c r="E5" t="n">
-        <v>486.0653128268237</v>
+        <v>1041.702847859838</v>
       </c>
       <c r="F5" t="n">
-        <v>481.126293929842</v>
+        <v>1036.763828962857</v>
       </c>
       <c r="G5" t="n">
-        <v>477.3309683874014</v>
+        <v>628.9280993800121</v>
       </c>
       <c r="H5" t="n">
-        <v>65.2</v>
+        <v>216.7971309926107</v>
       </c>
       <c r="I5" t="n">
         <v>65.2</v>
@@ -4561,49 +4561,49 @@
         <v>448.0719498394611</v>
       </c>
       <c r="K5" t="n">
-        <v>1155.805906933501</v>
+        <v>940.6648775060032</v>
       </c>
       <c r="L5" t="n">
-        <v>1140.066629078932</v>
+        <v>924.2825542736798</v>
       </c>
       <c r="M5" t="n">
-        <v>1644.905435046624</v>
+        <v>1429.121360241372</v>
       </c>
       <c r="N5" t="n">
-        <v>2254.194287995062</v>
+        <v>2038.410213189809</v>
       </c>
       <c r="O5" t="n">
-        <v>3061.044287995061</v>
+        <v>2845.260213189809</v>
       </c>
       <c r="P5" t="n">
-        <v>3260</v>
+        <v>2828.877889957487</v>
       </c>
       <c r="Q5" t="n">
         <v>3260</v>
       </c>
       <c r="R5" t="n">
-        <v>3161.565463247056</v>
+        <v>3006.587273910814</v>
       </c>
       <c r="S5" t="n">
-        <v>2661.718829103295</v>
+        <v>2813.315960095906</v>
       </c>
       <c r="T5" t="n">
-        <v>2069.117231397675</v>
+        <v>2624.75476643069</v>
       </c>
       <c r="U5" t="n">
-        <v>1413.338143974836</v>
+        <v>2373.016083048255</v>
       </c>
       <c r="V5" t="n">
-        <v>1181.165392291176</v>
+        <v>2140.843331364595</v>
       </c>
       <c r="W5" t="n">
-        <v>940.3841034215316</v>
+        <v>1900.062042494951</v>
       </c>
       <c r="X5" t="n">
-        <v>746.1600292188369</v>
+        <v>1705.837968292256</v>
       </c>
       <c r="Y5" t="n">
-        <v>633.718178024083</v>
+        <v>1593.396117097502</v>
       </c>
     </row>
     <row r="6">
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>139.10814922939</v>
+        <v>123.5087114984068</v>
       </c>
       <c r="C6" t="n">
-        <v>139.10814922939</v>
+        <v>123.5087114984068</v>
       </c>
       <c r="D6" t="n">
         <v>65.2</v>
@@ -4676,13 +4676,13 @@
         <v>580.3126330693322</v>
       </c>
       <c r="W6" t="n">
-        <v>547.61248871597</v>
+        <v>143.5720846755659</v>
       </c>
       <c r="X6" t="n">
-        <v>527.5491155388108</v>
+        <v>123.5087114984068</v>
       </c>
       <c r="Y6" t="n">
-        <v>527.5491155388108</v>
+        <v>123.5087114984068</v>
       </c>
     </row>
     <row r="7">
@@ -4692,28 +4692,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>520.8923659921371</v>
+        <v>440.0757524108052</v>
       </c>
       <c r="C7" t="n">
-        <v>646.8943718105729</v>
+        <v>566.077758229241</v>
       </c>
       <c r="D7" t="n">
-        <v>760.213515935573</v>
+        <v>679.3969023542411</v>
       </c>
       <c r="E7" t="n">
-        <v>878.042420146986</v>
+        <v>797.2258065656541</v>
       </c>
       <c r="F7" t="n">
-        <v>1002.403392738922</v>
+        <v>921.5867791575896</v>
       </c>
       <c r="G7" t="n">
-        <v>1002.403392738922</v>
+        <v>1074.993345044475</v>
       </c>
       <c r="H7" t="n">
-        <v>1002.403392738922</v>
+        <v>1244.509930203872</v>
       </c>
       <c r="I7" t="n">
-        <v>1223.536271675004</v>
+        <v>1465.642809139955</v>
       </c>
       <c r="J7" t="n">
         <v>1465.642809139955</v>
@@ -4746,22 +4746,22 @@
         <v>102.4502550941731</v>
       </c>
       <c r="T7" t="n">
-        <v>102.4502550941731</v>
+        <v>216.9091140654808</v>
       </c>
       <c r="U7" t="n">
-        <v>349.0014477324597</v>
+        <v>216.9091140654808</v>
       </c>
       <c r="V7" t="n">
-        <v>349.0014477324597</v>
+        <v>216.9091140654808</v>
       </c>
       <c r="W7" t="n">
-        <v>520.8923659921371</v>
+        <v>216.9091140654808</v>
       </c>
       <c r="X7" t="n">
-        <v>520.8923659921371</v>
+        <v>216.9091140654808</v>
       </c>
       <c r="Y7" t="n">
-        <v>520.8923659921371</v>
+        <v>328.3184147445131</v>
       </c>
     </row>
     <row r="8">
@@ -4771,22 +4771,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1510.568528253488</v>
+        <v>702.4877201726792</v>
       </c>
       <c r="C8" t="n">
-        <v>1460.594206795918</v>
+        <v>652.5133987151096</v>
       </c>
       <c r="D8" t="n">
-        <v>1046.1102110991</v>
+        <v>642.0698070586957</v>
       </c>
       <c r="E8" t="n">
-        <v>1041.702847859839</v>
+        <v>637.6624438194344</v>
       </c>
       <c r="F8" t="n">
         <v>632.7234249224528</v>
       </c>
       <c r="G8" t="n">
-        <v>628.9280993800121</v>
+        <v>224.8876953396081</v>
       </c>
       <c r="H8" t="n">
         <v>216.7971309926107</v>
@@ -4798,19 +4798,19 @@
         <v>448.0719498394611</v>
       </c>
       <c r="K8" t="n">
-        <v>1155.805906933501</v>
+        <v>638.9378729139711</v>
       </c>
       <c r="L8" t="n">
-        <v>1962.655906933501</v>
+        <v>1445.787872913971</v>
       </c>
       <c r="M8" t="n">
-        <v>1946.273583701177</v>
+        <v>1429.405549681648</v>
       </c>
       <c r="N8" t="n">
-        <v>2555.562436649614</v>
+        <v>2038.694402630085</v>
       </c>
       <c r="O8" t="n">
-        <v>2507.509320716978</v>
+        <v>2845.544402630085</v>
       </c>
       <c r="P8" t="n">
         <v>2828.877889957487</v>
@@ -4819,28 +4819,28 @@
         <v>3260</v>
       </c>
       <c r="R8" t="n">
-        <v>3006.587273910814</v>
+        <v>3260</v>
       </c>
       <c r="S8" t="n">
-        <v>2910.781043807457</v>
+        <v>2760.153365856239</v>
       </c>
       <c r="T8" t="n">
-        <v>2722.219850142241</v>
+        <v>2167.551768150619</v>
       </c>
       <c r="U8" t="n">
-        <v>2470.481166759806</v>
+        <v>1564.935274967447</v>
       </c>
       <c r="V8" t="n">
-        <v>2238.308415076146</v>
+        <v>1332.762523283786</v>
       </c>
       <c r="W8" t="n">
-        <v>1997.527126206502</v>
+        <v>1091.981234414142</v>
       </c>
       <c r="X8" t="n">
-        <v>1803.303052003807</v>
+        <v>897.7571602114477</v>
       </c>
       <c r="Y8" t="n">
-        <v>1593.396117097502</v>
+        <v>785.3153090166938</v>
       </c>
     </row>
     <row r="9">
@@ -4850,19 +4850,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>528.1638703204933</v>
+        <v>756.7619790837808</v>
       </c>
       <c r="C9" t="n">
-        <v>528.1638703204933</v>
+        <v>756.7619790837808</v>
       </c>
       <c r="D9" t="n">
-        <v>408.2669114524009</v>
+        <v>756.7619790837808</v>
       </c>
       <c r="E9" t="n">
-        <v>408.2669114524009</v>
+        <v>737.2967456696003</v>
       </c>
       <c r="F9" t="n">
-        <v>65.2</v>
+        <v>394.2298342171994</v>
       </c>
       <c r="G9" t="n">
         <v>65.2</v>
@@ -4895,31 +4895,31 @@
         <v>1220.632420368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1220.632420368536</v>
+        <v>1045.804879873102</v>
       </c>
       <c r="R9" t="n">
-        <v>1071.871008962092</v>
+        <v>897.0434684666577</v>
       </c>
       <c r="S9" t="n">
-        <v>1004.634645361474</v>
+        <v>829.8071048660403</v>
       </c>
       <c r="T9" t="n">
-        <v>999.2227613033796</v>
+        <v>824.3952208079455</v>
       </c>
       <c r="U9" t="n">
-        <v>999.0102766971303</v>
+        <v>824.1827362016962</v>
       </c>
       <c r="V9" t="n">
-        <v>984.3530371097362</v>
+        <v>809.5254966143021</v>
       </c>
       <c r="W9" t="n">
-        <v>951.6528927563741</v>
+        <v>776.82535226094</v>
       </c>
       <c r="X9" t="n">
-        <v>931.5895195792149</v>
+        <v>756.7619790837808</v>
       </c>
       <c r="Y9" t="n">
-        <v>528.1638703204933</v>
+        <v>756.7619790837808</v>
       </c>
     </row>
     <row r="10">
@@ -4929,28 +4929,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>668.3167733162213</v>
+        <v>847.6558574435028</v>
       </c>
       <c r="C10" t="n">
-        <v>668.3167733162213</v>
+        <v>921.5867791575896</v>
       </c>
       <c r="D10" t="n">
-        <v>781.6359174412214</v>
+        <v>921.5867791575896</v>
       </c>
       <c r="E10" t="n">
-        <v>781.6359174412214</v>
+        <v>921.5867791575896</v>
       </c>
       <c r="F10" t="n">
-        <v>781.6359174412214</v>
+        <v>921.5867791575896</v>
       </c>
       <c r="G10" t="n">
-        <v>935.0424833281066</v>
+        <v>1074.993345044475</v>
       </c>
       <c r="H10" t="n">
-        <v>1104.559068487504</v>
+        <v>1244.509930203872</v>
       </c>
       <c r="I10" t="n">
-        <v>1104.559068487504</v>
+        <v>1465.642809139955</v>
       </c>
       <c r="J10" t="n">
         <v>1465.642809139955</v>
@@ -4980,25 +4980,25 @@
         <v>65.2</v>
       </c>
       <c r="S10" t="n">
-        <v>65.2</v>
+        <v>102.4502550941731</v>
       </c>
       <c r="T10" t="n">
-        <v>65.2</v>
+        <v>290.525934252978</v>
       </c>
       <c r="U10" t="n">
-        <v>65.2</v>
+        <v>537.0771268912647</v>
       </c>
       <c r="V10" t="n">
-        <v>264.0213928859459</v>
+        <v>735.8985197772106</v>
       </c>
       <c r="W10" t="n">
-        <v>435.9123111456233</v>
+        <v>735.8985197772106</v>
       </c>
       <c r="X10" t="n">
-        <v>586.9431021698168</v>
+        <v>735.8985197772106</v>
       </c>
       <c r="Y10" t="n">
-        <v>668.3167733162213</v>
+        <v>735.8985197772106</v>
       </c>
     </row>
     <row r="11">
@@ -5008,22 +5008,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>421.1649250963513</v>
+        <v>664.0115077640112</v>
       </c>
       <c r="C11" t="n">
-        <v>421.1649250963513</v>
+        <v>437.2695095387649</v>
       </c>
       <c r="D11" t="n">
-        <v>233.9536566722606</v>
+        <v>250.0582411146742</v>
       </c>
       <c r="E11" t="n">
-        <v>233.9536566722606</v>
+        <v>250.0582411146742</v>
       </c>
       <c r="F11" t="n">
-        <v>233.9536566722606</v>
+        <v>250.0582411146742</v>
       </c>
       <c r="G11" t="n">
-        <v>233.9536566722606</v>
+        <v>250.0582411146742</v>
       </c>
       <c r="H11" t="n">
         <v>65.2</v>
@@ -5032,52 +5032,52 @@
         <v>65.2</v>
       </c>
       <c r="J11" t="n">
-        <v>456.5091130376557</v>
+        <v>180.775390095766</v>
       </c>
       <c r="K11" t="n">
-        <v>1166.215479385524</v>
+        <v>890.4817564436344</v>
       </c>
       <c r="L11" t="n">
-        <v>1166.215479385524</v>
+        <v>1697.331756443634</v>
       </c>
       <c r="M11" t="n">
-        <v>1166.215479385524</v>
+        <v>2208.180585172569</v>
       </c>
       <c r="N11" t="n">
-        <v>1779.435799160287</v>
+        <v>2821.400904947332</v>
       </c>
       <c r="O11" t="n">
-        <v>2453.15</v>
+        <v>2821.400904947332</v>
       </c>
       <c r="P11" t="n">
-        <v>3260</v>
+        <v>2821.400904947332</v>
       </c>
       <c r="Q11" t="n">
         <v>3260</v>
       </c>
       <c r="R11" t="n">
-        <v>3233.860001183541</v>
+        <v>3260</v>
       </c>
       <c r="S11" t="n">
-        <v>2961.286094312508</v>
+        <v>3204.132676980168</v>
       </c>
       <c r="T11" t="n">
-        <v>2595.957223879615</v>
+        <v>2838.803806547275</v>
       </c>
       <c r="U11" t="n">
-        <v>2167.450863729503</v>
+        <v>2410.297446397163</v>
       </c>
       <c r="V11" t="n">
-        <v>1758.510435278166</v>
+        <v>2001.357017945826</v>
       </c>
       <c r="W11" t="n">
-        <v>1340.961469640845</v>
+        <v>1583.808052308505</v>
       </c>
       <c r="X11" t="n">
-        <v>969.9697186704734</v>
+        <v>1212.816301338133</v>
       </c>
       <c r="Y11" t="n">
-        <v>680.7601907080427</v>
+        <v>923.6067733757027</v>
       </c>
     </row>
     <row r="12">
@@ -5111,7 +5111,7 @@
         <v>72.99487796756496</v>
       </c>
       <c r="J12" t="n">
-        <v>419.7013981428639</v>
+        <v>215.8771006891148</v>
       </c>
       <c r="K12" t="n">
         <v>627.8199167834982</v>
@@ -5169,46 +5169,46 @@
         <v>177.5115880782802</v>
       </c>
       <c r="C13" t="n">
-        <v>129.3042682317704</v>
+        <v>177.5115880782802</v>
       </c>
       <c r="D13" t="n">
-        <v>115.0816726946888</v>
+        <v>177.5115880782802</v>
       </c>
       <c r="E13" t="n">
-        <v>115.0816726946888</v>
+        <v>177.5115880782802</v>
       </c>
       <c r="F13" t="n">
-        <v>65.2</v>
+        <v>177.5115880782802</v>
       </c>
       <c r="G13" t="n">
-        <v>65.2</v>
+        <v>177.5115880782802</v>
       </c>
       <c r="H13" t="n">
-        <v>65.2</v>
+        <v>173.7023697938169</v>
       </c>
       <c r="I13" t="n">
-        <v>113.0828789360829</v>
+        <v>221.5852487298998</v>
       </c>
       <c r="J13" t="n">
-        <v>300.9166195885342</v>
+        <v>409.4189893823511</v>
       </c>
       <c r="K13" t="n">
-        <v>236.7542218096019</v>
+        <v>409.4189893823511</v>
       </c>
       <c r="L13" t="n">
-        <v>236.7542218096019</v>
+        <v>409.4189893823511</v>
       </c>
       <c r="M13" t="n">
-        <v>236.7542218096019</v>
+        <v>409.4189893823511</v>
       </c>
       <c r="N13" t="n">
-        <v>236.7542218096019</v>
+        <v>409.4189893823511</v>
       </c>
       <c r="O13" t="n">
-        <v>236.7542218096019</v>
+        <v>409.4189893823511</v>
       </c>
       <c r="P13" t="n">
-        <v>65.2</v>
+        <v>409.4189893823511</v>
       </c>
       <c r="Q13" t="n">
         <v>65.2</v>
@@ -5245,46 +5245,46 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>883.6685602764463</v>
+        <v>880.1835184729979</v>
       </c>
       <c r="C14" t="n">
-        <v>711.4720165966545</v>
+        <v>707.9869747932061</v>
       </c>
       <c r="D14" t="n">
-        <v>578.8062027180183</v>
+        <v>575.3211609145699</v>
       </c>
       <c r="E14" t="n">
-        <v>452.1766172565348</v>
+        <v>448.6915754530864</v>
       </c>
       <c r="F14" t="n">
-        <v>325.0153761373309</v>
+        <v>321.5303343338825</v>
       </c>
       <c r="G14" t="n">
-        <v>198.9978283726681</v>
+        <v>195.5127865692196</v>
       </c>
       <c r="H14" t="n">
-        <v>68.68504180344846</v>
+        <v>65.2</v>
       </c>
       <c r="I14" t="n">
         <v>65.2</v>
       </c>
       <c r="J14" t="n">
-        <v>129.7436336521319</v>
+        <v>65.2</v>
       </c>
       <c r="K14" t="n">
-        <v>839.4500000000003</v>
+        <v>774.9063663478685</v>
       </c>
       <c r="L14" t="n">
-        <v>1646.3</v>
+        <v>1329.080851496302</v>
       </c>
       <c r="M14" t="n">
-        <v>1646.3</v>
+        <v>1839.929680225237</v>
       </c>
       <c r="N14" t="n">
-        <v>1646.3</v>
+        <v>2453.15</v>
       </c>
       <c r="O14" t="n">
-        <v>2453.15</v>
+        <v>3260</v>
       </c>
       <c r="P14" t="n">
         <v>3260</v>
@@ -5293,28 +5293,28 @@
         <v>3260</v>
       </c>
       <c r="R14" t="n">
-        <v>3260</v>
+        <v>3256.514958196551</v>
       </c>
       <c r="S14" t="n">
-        <v>3041.971547674421</v>
+        <v>3038.486505870972</v>
       </c>
       <c r="T14" t="n">
-        <v>2731.188131786983</v>
+        <v>2727.703089983534</v>
       </c>
       <c r="U14" t="n">
-        <v>2357.227226182325</v>
+        <v>2353.742184378877</v>
       </c>
       <c r="V14" t="n">
-        <v>2002.832252276443</v>
+        <v>1999.347210472994</v>
       </c>
       <c r="W14" t="n">
-        <v>1639.828741184576</v>
+        <v>1636.343699381128</v>
       </c>
       <c r="X14" t="n">
-        <v>1323.382444759659</v>
+        <v>1319.897402956211</v>
       </c>
       <c r="Y14" t="n">
-        <v>1088.718371342683</v>
+        <v>1085.233329539235</v>
       </c>
     </row>
     <row r="15">
@@ -5351,16 +5351,16 @@
         <v>189.156520175299</v>
       </c>
       <c r="K15" t="n">
-        <v>654.5593362696824</v>
+        <v>378.3493362696823</v>
       </c>
       <c r="L15" t="n">
-        <v>925.9097978648824</v>
+        <v>693.7200877573046</v>
       </c>
       <c r="M15" t="n">
-        <v>1288.200339607742</v>
+        <v>1056.010629500164</v>
       </c>
       <c r="N15" t="n">
-        <v>1421.48062421531</v>
+        <v>1465.500914107732</v>
       </c>
       <c r="O15" t="n">
         <v>1704.543365791451</v>
@@ -5403,49 +5403,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>405.873354586564</v>
+        <v>422.6199739669084</v>
       </c>
       <c r="C16" t="n">
-        <v>412.0853604049998</v>
+        <v>428.8319797853442</v>
       </c>
       <c r="D16" t="n">
-        <v>405.4831199448427</v>
+        <v>428.8319797853442</v>
       </c>
       <c r="E16" t="n">
-        <v>403.4822059681189</v>
+        <v>428.8319797853442</v>
       </c>
       <c r="F16" t="n">
-        <v>408.0531785600544</v>
+        <v>433.4029523772797</v>
       </c>
       <c r="G16" t="n">
-        <v>441.6697444469397</v>
+        <v>467.019518264165</v>
       </c>
       <c r="H16" t="n">
-        <v>491.3963296063373</v>
+        <v>516.7461034235625</v>
       </c>
       <c r="I16" t="n">
-        <v>592.7392085424202</v>
+        <v>618.0889823596455</v>
       </c>
       <c r="J16" t="n">
-        <v>834.0329491948715</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="K16" t="n">
-        <v>834.0329491948715</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="L16" t="n">
-        <v>688.0252439849936</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="M16" t="n">
-        <v>688.0252439849936</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="N16" t="n">
-        <v>688.0252439849936</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="O16" t="n">
-        <v>477.7736336649268</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="P16" t="n">
-        <v>65.2</v>
+        <v>516.552794369291</v>
       </c>
       <c r="Q16" t="n">
         <v>65.2</v>
@@ -5472,7 +5472,7 @@
         <v>422.6199739669084</v>
       </c>
       <c r="Y16" t="n">
-        <v>414.0691125028051</v>
+        <v>422.6199739669084</v>
       </c>
     </row>
     <row r="17">
@@ -5482,16 +5482,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>880.1835184729979</v>
+        <v>883.6685602764463</v>
       </c>
       <c r="C17" t="n">
-        <v>707.9869747932061</v>
+        <v>711.4720165966545</v>
       </c>
       <c r="D17" t="n">
-        <v>575.3211609145699</v>
+        <v>578.8062027180183</v>
       </c>
       <c r="E17" t="n">
-        <v>448.6915754530864</v>
+        <v>452.1766172565348</v>
       </c>
       <c r="F17" t="n">
         <v>321.5303343338825</v>
@@ -5506,25 +5506,25 @@
         <v>65.2</v>
       </c>
       <c r="J17" t="n">
-        <v>456.5091130376557</v>
+        <v>65.2</v>
       </c>
       <c r="K17" t="n">
-        <v>1166.215479385524</v>
+        <v>774.9063663478685</v>
       </c>
       <c r="L17" t="n">
-        <v>1166.215479385524</v>
+        <v>1581.756366347868</v>
       </c>
       <c r="M17" t="n">
-        <v>1166.215479385524</v>
+        <v>2092.605195076803</v>
       </c>
       <c r="N17" t="n">
-        <v>1646.3</v>
+        <v>2705.825514851566</v>
       </c>
       <c r="O17" t="n">
-        <v>2453.15</v>
+        <v>2705.825514851566</v>
       </c>
       <c r="P17" t="n">
-        <v>3260</v>
+        <v>2821.400904947332</v>
       </c>
       <c r="Q17" t="n">
         <v>3260</v>
@@ -5533,25 +5533,25 @@
         <v>3260</v>
       </c>
       <c r="S17" t="n">
-        <v>3038.486505870972</v>
+        <v>3041.971547674421</v>
       </c>
       <c r="T17" t="n">
-        <v>2727.703089983534</v>
+        <v>2731.188131786983</v>
       </c>
       <c r="U17" t="n">
-        <v>2353.742184378877</v>
+        <v>2357.227226182325</v>
       </c>
       <c r="V17" t="n">
-        <v>1999.347210472994</v>
+        <v>2002.832252276443</v>
       </c>
       <c r="W17" t="n">
-        <v>1636.343699381128</v>
+        <v>1639.828741184576</v>
       </c>
       <c r="X17" t="n">
-        <v>1319.897402956211</v>
+        <v>1323.382444759659</v>
       </c>
       <c r="Y17" t="n">
-        <v>1085.233329539235</v>
+        <v>1088.718371342683</v>
       </c>
     </row>
     <row r="18">
@@ -5582,25 +5582,25 @@
         <v>65.2</v>
       </c>
       <c r="I18" t="n">
-        <v>109.2202898924221</v>
+        <v>65.2</v>
       </c>
       <c r="J18" t="n">
-        <v>233.176810067721</v>
+        <v>465.3665201752989</v>
       </c>
       <c r="K18" t="n">
-        <v>698.5796261621044</v>
+        <v>930.7693362696823</v>
       </c>
       <c r="L18" t="n">
-        <v>969.9300877573045</v>
+        <v>1202.119797864882</v>
       </c>
       <c r="M18" t="n">
-        <v>1056.010629500164</v>
+        <v>1288.200339607742</v>
       </c>
       <c r="N18" t="n">
-        <v>1465.500914107732</v>
+        <v>1421.48062421531</v>
       </c>
       <c r="O18" t="n">
-        <v>1704.543365791451</v>
+        <v>1660.523075899029</v>
       </c>
       <c r="P18" t="n">
         <v>1817.072710260958</v>
@@ -5646,43 +5646,43 @@
         <v>428.8319797853442</v>
       </c>
       <c r="D19" t="n">
-        <v>422.2297393251872</v>
+        <v>428.8319797853442</v>
       </c>
       <c r="E19" t="n">
-        <v>422.2297393251872</v>
+        <v>428.8319797853442</v>
       </c>
       <c r="F19" t="n">
-        <v>426.8007119171227</v>
+        <v>433.4029523772797</v>
       </c>
       <c r="G19" t="n">
-        <v>460.4172778040079</v>
+        <v>467.019518264165</v>
       </c>
       <c r="H19" t="n">
-        <v>510.1438629634055</v>
+        <v>516.7461034235625</v>
       </c>
       <c r="I19" t="n">
-        <v>611.4867418994884</v>
+        <v>618.0889823596455</v>
       </c>
       <c r="J19" t="n">
-        <v>852.7804825519397</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="K19" t="n">
-        <v>852.7804825519397</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="L19" t="n">
-        <v>852.7804825519397</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="M19" t="n">
-        <v>852.7804825519397</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="N19" t="n">
-        <v>557.644042883571</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="O19" t="n">
-        <v>557.644042883571</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="P19" t="n">
-        <v>517.3233615971224</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="Q19" t="n">
         <v>517.3233615971224</v>
@@ -5743,25 +5743,25 @@
         <v>65.2</v>
       </c>
       <c r="J20" t="n">
-        <v>65.2</v>
+        <v>456.5091130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>774.9063663478685</v>
+        <v>1166.215479385524</v>
       </c>
       <c r="L20" t="n">
-        <v>1581.756366347868</v>
+        <v>1942.301171271065</v>
       </c>
       <c r="M20" t="n">
-        <v>1581.756366347868</v>
+        <v>2453.15</v>
       </c>
       <c r="N20" t="n">
-        <v>2194.976686122632</v>
+        <v>2453.15</v>
       </c>
       <c r="O20" t="n">
-        <v>3001.826686122632</v>
+        <v>2453.15</v>
       </c>
       <c r="P20" t="n">
-        <v>3001.826686122632</v>
+        <v>3260</v>
       </c>
       <c r="Q20" t="n">
         <v>3260</v>
@@ -5819,28 +5819,28 @@
         <v>65.2</v>
       </c>
       <c r="I21" t="n">
-        <v>65.2</v>
+        <v>126.454877967565</v>
       </c>
       <c r="J21" t="n">
-        <v>465.3665201752989</v>
+        <v>250.4113981428639</v>
       </c>
       <c r="K21" t="n">
-        <v>654.5593362696823</v>
+        <v>439.6042142372473</v>
       </c>
       <c r="L21" t="n">
-        <v>925.9097978648824</v>
+        <v>710.9546758324475</v>
       </c>
       <c r="M21" t="n">
-        <v>1056.010629500164</v>
+        <v>951.1491019397386</v>
       </c>
       <c r="N21" t="n">
-        <v>1189.290914107732</v>
+        <v>1084.429386547307</v>
       </c>
       <c r="O21" t="n">
-        <v>1428.333365791451</v>
+        <v>1599.681838231026</v>
       </c>
       <c r="P21" t="n">
-        <v>1817.072710260958</v>
+        <v>1712.211182700533</v>
       </c>
       <c r="Q21" t="n">
         <v>1817.072710260958</v>
@@ -5913,19 +5913,19 @@
         <v>859.3827230120968</v>
       </c>
       <c r="N22" t="n">
-        <v>564.2462833437282</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="O22" t="n">
-        <v>561.9892697284172</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="P22" t="n">
-        <v>149.4156360634904</v>
+        <v>446.80908934717</v>
       </c>
       <c r="Q22" t="n">
-        <v>149.4156360634904</v>
+        <v>65.2</v>
       </c>
       <c r="R22" t="n">
-        <v>149.4156360634904</v>
+        <v>65.2</v>
       </c>
       <c r="S22" t="n">
         <v>65.2</v>
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>880.1835184729979</v>
+        <v>883.6685602764463</v>
       </c>
       <c r="C23" t="n">
-        <v>707.9869747932061</v>
+        <v>711.4720165966545</v>
       </c>
       <c r="D23" t="n">
-        <v>575.3211609145699</v>
+        <v>578.8062027180183</v>
       </c>
       <c r="E23" t="n">
-        <v>448.6915754530864</v>
+        <v>452.1766172565348</v>
       </c>
       <c r="F23" t="n">
-        <v>321.5303343338825</v>
+        <v>325.0153761373309</v>
       </c>
       <c r="G23" t="n">
-        <v>195.5127865692196</v>
+        <v>198.9978283726681</v>
       </c>
       <c r="H23" t="n">
         <v>65.2</v>
@@ -5986,46 +5986,46 @@
         <v>1166.215479385524</v>
       </c>
       <c r="L23" t="n">
-        <v>1973.065479385524</v>
+        <v>1329.080851496302</v>
       </c>
       <c r="M23" t="n">
-        <v>2483.914308114459</v>
+        <v>1839.929680225237</v>
       </c>
       <c r="N23" t="n">
-        <v>2483.914308114459</v>
+        <v>2453.15</v>
       </c>
       <c r="O23" t="n">
-        <v>2483.914308114459</v>
+        <v>2453.15</v>
       </c>
       <c r="P23" t="n">
-        <v>2821.400904947332</v>
+        <v>3260</v>
       </c>
       <c r="Q23" t="n">
         <v>3260</v>
       </c>
       <c r="R23" t="n">
-        <v>3256.514958196551</v>
+        <v>3260</v>
       </c>
       <c r="S23" t="n">
-        <v>3038.486505870972</v>
+        <v>3041.971547674421</v>
       </c>
       <c r="T23" t="n">
-        <v>2727.703089983534</v>
+        <v>2731.188131786983</v>
       </c>
       <c r="U23" t="n">
-        <v>2353.742184378877</v>
+        <v>2357.227226182325</v>
       </c>
       <c r="V23" t="n">
-        <v>1999.347210472994</v>
+        <v>2002.832252276443</v>
       </c>
       <c r="W23" t="n">
-        <v>1636.343699381128</v>
+        <v>1639.828741184576</v>
       </c>
       <c r="X23" t="n">
-        <v>1319.897402956211</v>
+        <v>1323.382444759659</v>
       </c>
       <c r="Y23" t="n">
-        <v>1085.233329539235</v>
+        <v>1088.718371342683</v>
       </c>
     </row>
     <row r="24">
@@ -6056,28 +6056,28 @@
         <v>65.2</v>
       </c>
       <c r="I24" t="n">
-        <v>65.2</v>
+        <v>126.454877967565</v>
       </c>
       <c r="J24" t="n">
-        <v>233.1768100677209</v>
+        <v>250.4113981428639</v>
       </c>
       <c r="K24" t="n">
-        <v>422.3696261621043</v>
+        <v>439.6042142372473</v>
       </c>
       <c r="L24" t="n">
-        <v>969.9300877573045</v>
+        <v>710.9546758324475</v>
       </c>
       <c r="M24" t="n">
-        <v>1056.010629500164</v>
+        <v>797.0352175753068</v>
       </c>
       <c r="N24" t="n">
-        <v>1189.290914107732</v>
+        <v>930.3155021828751</v>
       </c>
       <c r="O24" t="n">
-        <v>1428.333365791451</v>
+        <v>1323.471838231026</v>
       </c>
       <c r="P24" t="n">
-        <v>1817.072710260958</v>
+        <v>1712.211182700533</v>
       </c>
       <c r="Q24" t="n">
         <v>1817.072710260958</v>
@@ -6120,46 +6120,46 @@
         <v>428.8319797853442</v>
       </c>
       <c r="D25" t="n">
-        <v>422.2297393251872</v>
+        <v>428.8319797853442</v>
       </c>
       <c r="E25" t="n">
-        <v>420.2288253484634</v>
+        <v>428.8319797853442</v>
       </c>
       <c r="F25" t="n">
-        <v>424.7997979403989</v>
+        <v>433.4029523772797</v>
       </c>
       <c r="G25" t="n">
-        <v>458.4163638272842</v>
+        <v>467.019518264165</v>
       </c>
       <c r="H25" t="n">
-        <v>508.1429489866817</v>
+        <v>516.7461034235625</v>
       </c>
       <c r="I25" t="n">
-        <v>609.4858279227647</v>
+        <v>618.0889823596455</v>
       </c>
       <c r="J25" t="n">
-        <v>850.779568575216</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="K25" t="n">
-        <v>841.1626253417381</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="L25" t="n">
-        <v>841.1626253417381</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="M25" t="n">
-        <v>841.1626253417381</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="N25" t="n">
-        <v>841.1626253417381</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="O25" t="n">
-        <v>841.1626253417381</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="P25" t="n">
-        <v>428.5889916768114</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="Q25" t="n">
-        <v>428.5889916768114</v>
+        <v>517.3233615971224</v>
       </c>
       <c r="R25" t="n">
         <v>65.2</v>
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1017.364977321634</v>
+        <v>277.1649250963515</v>
       </c>
       <c r="C26" t="n">
-        <v>790.622979096388</v>
+        <v>62.32</v>
       </c>
       <c r="D26" t="n">
-        <v>790.622979096388</v>
+        <v>62.32</v>
       </c>
       <c r="E26" t="n">
-        <v>609.44793908945</v>
+        <v>62.32</v>
       </c>
       <c r="F26" t="n">
-        <v>427.7412434247915</v>
+        <v>62.32</v>
       </c>
       <c r="G26" t="n">
-        <v>247.1782411146742</v>
+        <v>62.32</v>
       </c>
       <c r="H26" t="n">
         <v>62.32</v>
@@ -6220,19 +6220,19 @@
         <v>453.6291130376557</v>
       </c>
       <c r="K26" t="n">
-        <v>453.6291130376557</v>
+        <v>1163.335479385524</v>
       </c>
       <c r="L26" t="n">
-        <v>1220.720851496276</v>
+        <v>1163.335479385524</v>
       </c>
       <c r="M26" t="n">
-        <v>1731.569680225211</v>
+        <v>1674.184308114459</v>
       </c>
       <c r="N26" t="n">
-        <v>2344.789999999974</v>
+        <v>1674.184308114459</v>
       </c>
       <c r="O26" t="n">
-        <v>3116</v>
+        <v>2344.789999999975</v>
       </c>
       <c r="P26" t="n">
         <v>3116</v>
@@ -6253,16 +6253,16 @@
         <v>2023.450863729503</v>
       </c>
       <c r="V26" t="n">
-        <v>1983.718736533077</v>
+        <v>1614.510435278166</v>
       </c>
       <c r="W26" t="n">
-        <v>1566.169770895757</v>
+        <v>1196.961469640845</v>
       </c>
       <c r="X26" t="n">
-        <v>1566.169770895757</v>
+        <v>825.9697186704736</v>
       </c>
       <c r="Y26" t="n">
-        <v>1276.960242933326</v>
+        <v>536.760190708043</v>
       </c>
     </row>
     <row r="27">
@@ -6296,13 +6296,13 @@
         <v>70.11487796756495</v>
       </c>
       <c r="J27" t="n">
-        <v>416.8213981428639</v>
+        <v>212.9971006891147</v>
       </c>
       <c r="K27" t="n">
-        <v>828.7642142372474</v>
+        <v>624.9399167834981</v>
       </c>
       <c r="L27" t="n">
-        <v>1322.864675832448</v>
+        <v>1119.040378378698</v>
       </c>
       <c r="M27" t="n">
         <v>1427.870920121557</v>
@@ -6351,52 +6351,52 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>176.0182646830374</v>
+        <v>174.6315880782802</v>
       </c>
       <c r="C28" t="n">
-        <v>176.0182646830374</v>
+        <v>174.6315880782802</v>
       </c>
       <c r="D28" t="n">
-        <v>176.0182646830374</v>
+        <v>174.6315880782802</v>
       </c>
       <c r="E28" t="n">
-        <v>176.0182646830374</v>
+        <v>174.6315880782802</v>
       </c>
       <c r="F28" t="n">
-        <v>176.0182646830374</v>
+        <v>174.6315880782802</v>
       </c>
       <c r="G28" t="n">
-        <v>176.0182646830374</v>
+        <v>174.6315880782802</v>
       </c>
       <c r="H28" t="n">
-        <v>176.0182646830374</v>
+        <v>170.8223697938169</v>
       </c>
       <c r="I28" t="n">
-        <v>223.9011436191203</v>
+        <v>218.7052487298998</v>
       </c>
       <c r="J28" t="n">
-        <v>411.7348842715717</v>
+        <v>406.5389893823511</v>
       </c>
       <c r="K28" t="n">
-        <v>411.7348842715717</v>
+        <v>406.5389893823511</v>
       </c>
       <c r="L28" t="n">
-        <v>411.7348842715717</v>
+        <v>406.5389893823511</v>
       </c>
       <c r="M28" t="n">
-        <v>411.7348842715717</v>
+        <v>406.5389893823511</v>
       </c>
       <c r="N28" t="n">
-        <v>411.7348842715717</v>
+        <v>406.5389893823511</v>
       </c>
       <c r="O28" t="n">
-        <v>411.7348842715717</v>
+        <v>406.5389893823511</v>
       </c>
       <c r="P28" t="n">
-        <v>62.32</v>
+        <v>406.5389893823511</v>
       </c>
       <c r="Q28" t="n">
-        <v>62.32</v>
+        <v>406.5389893823511</v>
       </c>
       <c r="R28" t="n">
         <v>62.32</v>
@@ -6414,13 +6414,13 @@
         <v>176.0182646830374</v>
       </c>
       <c r="W28" t="n">
-        <v>176.0182646830374</v>
+        <v>174.6315880782802</v>
       </c>
       <c r="X28" t="n">
-        <v>176.0182646830374</v>
+        <v>174.6315880782802</v>
       </c>
       <c r="Y28" t="n">
-        <v>176.0182646830374</v>
+        <v>174.6315880782802</v>
       </c>
     </row>
     <row r="29">
@@ -6430,19 +6430,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1047.000488169968</v>
+        <v>513.4059340138206</v>
       </c>
       <c r="C29" t="n">
-        <v>846.5211162073476</v>
+        <v>513.4059340138206</v>
       </c>
       <c r="D29" t="n">
-        <v>685.5724740458832</v>
+        <v>352.4572918523561</v>
       </c>
       <c r="E29" t="n">
-        <v>530.6600603015713</v>
+        <v>352.4572918523561</v>
       </c>
       <c r="F29" t="n">
-        <v>375.2159908995391</v>
+        <v>220.9156148520479</v>
       </c>
       <c r="G29" t="n">
         <v>220.9156148520479</v>
@@ -6457,22 +6457,22 @@
         <v>453.6291130376557</v>
       </c>
       <c r="K29" t="n">
-        <v>1134.980904947262</v>
+        <v>1163.335479385524</v>
       </c>
       <c r="L29" t="n">
-        <v>1134.980904947262</v>
+        <v>1934.545479385524</v>
       </c>
       <c r="M29" t="n">
-        <v>1134.980904947262</v>
+        <v>2445.394308114459</v>
       </c>
       <c r="N29" t="n">
-        <v>1134.980904947262</v>
+        <v>3058.614627889222</v>
       </c>
       <c r="O29" t="n">
-        <v>1906.190904947297</v>
+        <v>3058.614627889222</v>
       </c>
       <c r="P29" t="n">
-        <v>2677.400904947332</v>
+        <v>3058.614627889222</v>
       </c>
       <c r="Q29" t="n">
         <v>3116</v>
@@ -6490,16 +6490,16 @@
         <v>2128.378741333841</v>
       </c>
       <c r="V29" t="n">
-        <v>1783.015952252407</v>
+        <v>1745.70093914513</v>
       </c>
       <c r="W29" t="n">
-        <v>1391.729612877713</v>
+        <v>1354.414599770435</v>
       </c>
       <c r="X29" t="n">
-        <v>1047.000488169968</v>
+        <v>1009.68547506269</v>
       </c>
       <c r="Y29" t="n">
-        <v>1047.000488169968</v>
+        <v>746.7385733628857</v>
       </c>
     </row>
     <row r="30">
@@ -6530,28 +6530,28 @@
         <v>62.32</v>
       </c>
       <c r="I30" t="n">
-        <v>89.0427141348467</v>
+        <v>95.85487796756496</v>
       </c>
       <c r="J30" t="n">
-        <v>212.9992343101457</v>
+        <v>219.8113981428639</v>
       </c>
       <c r="K30" t="n">
-        <v>650.682050404529</v>
+        <v>409.0042142372473</v>
       </c>
       <c r="L30" t="n">
-        <v>922.0325119997292</v>
+        <v>680.3546758324474</v>
       </c>
       <c r="M30" t="n">
-        <v>1256.603053742588</v>
+        <v>1014.925217575307</v>
       </c>
       <c r="N30" t="n">
-        <v>1638.373338350157</v>
+        <v>1312.741810789732</v>
       </c>
       <c r="O30" t="n">
-        <v>1877.415790033876</v>
+        <v>1800.27426247345</v>
       </c>
       <c r="P30" t="n">
-        <v>2238.435134503382</v>
+        <v>2161.293606942957</v>
       </c>
       <c r="Q30" t="n">
         <v>2238.435134503382</v>
@@ -6624,10 +6624,10 @@
         <v>596.2397446017254</v>
       </c>
       <c r="N31" t="n">
-        <v>596.2397446017254</v>
+        <v>542.7261898799507</v>
       </c>
       <c r="O31" t="n">
-        <v>596.2397446017254</v>
+        <v>542.7261898799507</v>
       </c>
       <c r="P31" t="n">
         <v>542.7261898799507</v>
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>812.3958330037195</v>
+        <v>822.7580639275434</v>
       </c>
       <c r="C32" t="n">
-        <v>649.2901984148368</v>
+        <v>659.6524293386606</v>
       </c>
       <c r="D32" t="n">
         <v>536.0775245509335</v>
@@ -6691,22 +6691,22 @@
         <v>62.32</v>
       </c>
       <c r="J32" t="n">
-        <v>62.32</v>
+        <v>453.6291130376557</v>
       </c>
       <c r="K32" t="n">
-        <v>771.0647617334017</v>
+        <v>1162.373874771058</v>
       </c>
       <c r="L32" t="n">
-        <v>1542.274761733402</v>
+        <v>1906.190904947287</v>
       </c>
       <c r="M32" t="n">
-        <v>1542.274761733402</v>
+        <v>1906.190904947287</v>
       </c>
       <c r="N32" t="n">
-        <v>2155.495081508165</v>
+        <v>1906.190904947287</v>
       </c>
       <c r="O32" t="n">
-        <v>2677.400904947332</v>
+        <v>1906.190904947287</v>
       </c>
       <c r="P32" t="n">
         <v>2677.400904947332</v>
@@ -6718,25 +6718,25 @@
         <v>3116</v>
       </c>
       <c r="S32" t="n">
-        <v>2907.06245676533</v>
+        <v>2917.424687689154</v>
       </c>
       <c r="T32" t="n">
-        <v>2605.369949968801</v>
+        <v>2615.732180892625</v>
       </c>
       <c r="U32" t="n">
-        <v>2240.499953455053</v>
+        <v>2250.862184378877</v>
       </c>
       <c r="V32" t="n">
-        <v>1895.195888640079</v>
+        <v>1905.558119563903</v>
       </c>
       <c r="W32" t="n">
-        <v>1541.283286639122</v>
+        <v>1551.645517562946</v>
       </c>
       <c r="X32" t="n">
-        <v>1233.927899305114</v>
+        <v>1244.290130228938</v>
       </c>
       <c r="Y32" t="n">
-        <v>1008.354734979047</v>
+        <v>1018.716965902871</v>
       </c>
     </row>
     <row r="33">
@@ -6767,28 +6767,28 @@
         <v>62.32</v>
       </c>
       <c r="I33" t="n">
-        <v>62.32</v>
+        <v>132.484877967565</v>
       </c>
       <c r="J33" t="n">
-        <v>186.2765201752989</v>
+        <v>256.4413981428639</v>
       </c>
       <c r="K33" t="n">
-        <v>375.4693362696823</v>
+        <v>445.6342142372473</v>
       </c>
       <c r="L33" t="n">
-        <v>646.8197978648825</v>
+        <v>716.9846758324475</v>
       </c>
       <c r="M33" t="n">
-        <v>732.9003396077418</v>
+        <v>803.0652175753067</v>
       </c>
       <c r="N33" t="n">
-        <v>1151.30062421531</v>
+        <v>936.3455021828751</v>
       </c>
       <c r="O33" t="n">
-        <v>1565.299729427815</v>
+        <v>1175.387953866594</v>
       </c>
       <c r="P33" t="n">
-        <v>1677.829073897321</v>
+        <v>1564.057546336896</v>
       </c>
       <c r="Q33" t="n">
         <v>1677.829073897321</v>
@@ -6855,25 +6855,25 @@
         <v>965.3074096938342</v>
       </c>
       <c r="L34" t="n">
-        <v>965.3074096938342</v>
+        <v>939.3525765184341</v>
       </c>
       <c r="M34" t="n">
-        <v>965.3074096938342</v>
+        <v>704.3711508592928</v>
       </c>
       <c r="N34" t="n">
-        <v>935.7122325327964</v>
+        <v>418.3256202818333</v>
       </c>
       <c r="O34" t="n">
-        <v>579.7066122509631</v>
+        <v>62.32</v>
       </c>
       <c r="P34" t="n">
-        <v>579.7066122509631</v>
+        <v>62.32</v>
       </c>
       <c r="Q34" t="n">
-        <v>137.4447269725813</v>
+        <v>62.32</v>
       </c>
       <c r="R34" t="n">
-        <v>137.4447269725813</v>
+        <v>62.32</v>
       </c>
       <c r="S34" t="n">
         <v>62.32</v>
@@ -6931,19 +6931,19 @@
         <v>453.6291130376557</v>
       </c>
       <c r="K35" t="n">
-        <v>453.6291130376557</v>
+        <v>1163.335479385524</v>
       </c>
       <c r="L35" t="n">
-        <v>1176.517273114743</v>
+        <v>1833.941171270995</v>
       </c>
       <c r="M35" t="n">
-        <v>1176.517273114743</v>
+        <v>2344.78999999993</v>
       </c>
       <c r="N35" t="n">
-        <v>1789.737592889506</v>
+        <v>2344.78999999993</v>
       </c>
       <c r="O35" t="n">
-        <v>2344.789999999934</v>
+        <v>3116</v>
       </c>
       <c r="P35" t="n">
         <v>3116</v>
@@ -6955,13 +6955,13 @@
         <v>3116</v>
       </c>
       <c r="S35" t="n">
-        <v>2917.424687689154</v>
+        <v>2907.06245676533</v>
       </c>
       <c r="T35" t="n">
-        <v>2615.732180892625</v>
+        <v>2605.369949968801</v>
       </c>
       <c r="U35" t="n">
-        <v>2250.862184378877</v>
+        <v>2240.499953455053</v>
       </c>
       <c r="V35" t="n">
         <v>1905.558119563903</v>
@@ -7004,28 +7004,28 @@
         <v>62.32</v>
       </c>
       <c r="I36" t="n">
-        <v>62.32</v>
+        <v>123.5051259683604</v>
       </c>
       <c r="J36" t="n">
-        <v>186.2765201752989</v>
+        <v>247.4616461436594</v>
       </c>
       <c r="K36" t="n">
-        <v>375.4693362696823</v>
+        <v>436.6544622380428</v>
       </c>
       <c r="L36" t="n">
-        <v>646.8197978648825</v>
+        <v>708.0049238332429</v>
       </c>
       <c r="M36" t="n">
-        <v>732.9003396077418</v>
+        <v>794.0854655761021</v>
       </c>
       <c r="N36" t="n">
-        <v>1041.137277744096</v>
+        <v>927.3657501836705</v>
       </c>
       <c r="O36" t="n">
-        <v>1280.179729427815</v>
+        <v>1166.408201867389</v>
       </c>
       <c r="P36" t="n">
-        <v>1677.829073897321</v>
+        <v>1564.057546336896</v>
       </c>
       <c r="Q36" t="n">
         <v>1677.829073897321</v>
@@ -7095,19 +7095,19 @@
         <v>965.3074096938342</v>
       </c>
       <c r="M37" t="n">
-        <v>821.8083448558509</v>
+        <v>965.3074096938342</v>
       </c>
       <c r="N37" t="n">
-        <v>821.8083448558509</v>
+        <v>965.3074096938342</v>
       </c>
       <c r="O37" t="n">
-        <v>465.8027245740176</v>
+        <v>965.3074096938342</v>
       </c>
       <c r="P37" t="n">
-        <v>62.32</v>
+        <v>561.8246851198165</v>
       </c>
       <c r="Q37" t="n">
-        <v>62.32</v>
+        <v>119.5627998414347</v>
       </c>
       <c r="R37" t="n">
         <v>62.32</v>
@@ -7165,22 +7165,22 @@
         <v>62.32</v>
       </c>
       <c r="J38" t="n">
-        <v>364.7325095618707</v>
+        <v>453.6291130376557</v>
       </c>
       <c r="K38" t="n">
-        <v>363.770904947161</v>
+        <v>1163.335479385524</v>
       </c>
       <c r="L38" t="n">
-        <v>1134.980904947161</v>
+        <v>1553.331756443634</v>
       </c>
       <c r="M38" t="n">
-        <v>1134.980904947161</v>
+        <v>2064.180585172569</v>
       </c>
       <c r="N38" t="n">
-        <v>1134.980904947161</v>
+        <v>2677.400904947332</v>
       </c>
       <c r="O38" t="n">
-        <v>1906.190904947247</v>
+        <v>2677.400904947332</v>
       </c>
       <c r="P38" t="n">
         <v>2677.400904947332</v>
@@ -7189,10 +7189,10 @@
         <v>3116</v>
       </c>
       <c r="R38" t="n">
-        <v>3116.000000000353</v>
+        <v>3116</v>
       </c>
       <c r="S38" t="n">
-        <v>2907.062456765684</v>
+        <v>2917.424687689154</v>
       </c>
       <c r="T38" t="n">
         <v>2615.732180892625</v>
@@ -7241,28 +7241,28 @@
         <v>62.32</v>
       </c>
       <c r="I39" t="n">
-        <v>62.32</v>
+        <v>123.5051259683604</v>
       </c>
       <c r="J39" t="n">
-        <v>186.2765201752989</v>
+        <v>247.4616461436594</v>
       </c>
       <c r="K39" t="n">
-        <v>375.4693362696823</v>
+        <v>436.6544622380428</v>
       </c>
       <c r="L39" t="n">
-        <v>646.8197978648825</v>
+        <v>708.0049238332429</v>
       </c>
       <c r="M39" t="n">
-        <v>732.9003396077418</v>
+        <v>794.0854655761021</v>
       </c>
       <c r="N39" t="n">
-        <v>1151.30062421531</v>
+        <v>927.3657501836705</v>
       </c>
       <c r="O39" t="n">
-        <v>1565.299729427815</v>
+        <v>1166.408201867389</v>
       </c>
       <c r="P39" t="n">
-        <v>1677.829073897321</v>
+        <v>1564.057546336896</v>
       </c>
       <c r="Q39" t="n">
         <v>1677.829073897321</v>
@@ -7329,25 +7329,25 @@
         <v>965.3074096938342</v>
       </c>
       <c r="L40" t="n">
-        <v>965.3074096938342</v>
+        <v>828.3906135748653</v>
       </c>
       <c r="M40" t="n">
-        <v>965.3074096938342</v>
+        <v>593.4091879157239</v>
       </c>
       <c r="N40" t="n">
-        <v>965.3074096938342</v>
+        <v>307.3636573382644</v>
       </c>
       <c r="O40" t="n">
-        <v>965.3074096938342</v>
+        <v>62.32</v>
       </c>
       <c r="P40" t="n">
-        <v>561.8246851198165</v>
+        <v>62.32</v>
       </c>
       <c r="Q40" t="n">
-        <v>119.5627998414347</v>
+        <v>62.32</v>
       </c>
       <c r="R40" t="n">
-        <v>119.5627998414347</v>
+        <v>62.32</v>
       </c>
       <c r="S40" t="n">
         <v>62.32</v>
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1386.394427563907</v>
+        <v>62.32</v>
       </c>
       <c r="C41" t="n">
-        <v>1129.34939903563</v>
+        <v>62.32</v>
       </c>
       <c r="D41" t="n">
-        <v>911.8351003085093</v>
+        <v>62.32</v>
       </c>
       <c r="E41" t="n">
-        <v>700.357029998541</v>
+        <v>62.32</v>
       </c>
       <c r="F41" t="n">
-        <v>488.3473040308522</v>
+        <v>62.32</v>
       </c>
       <c r="G41" t="n">
-        <v>277.4812714177045</v>
+        <v>62.32</v>
       </c>
       <c r="H41" t="n">
         <v>62.32</v>
@@ -7408,46 +7408,46 @@
         <v>1163.335479385524</v>
       </c>
       <c r="L41" t="n">
-        <v>1163.335479385524</v>
+        <v>1934.545479385524</v>
       </c>
       <c r="M41" t="n">
-        <v>1674.184308114459</v>
+        <v>2445.394308114459</v>
       </c>
       <c r="N41" t="n">
-        <v>2287.404627889222</v>
+        <v>3058.614627889222</v>
       </c>
       <c r="O41" t="n">
-        <v>2287.404627889222</v>
+        <v>3058.614627889222</v>
       </c>
       <c r="P41" t="n">
-        <v>2677.400904947332</v>
+        <v>3058.614627889222</v>
       </c>
       <c r="Q41" t="n">
         <v>3116</v>
       </c>
       <c r="R41" t="n">
-        <v>3116</v>
+        <v>3059.556970880511</v>
       </c>
       <c r="S41" t="n">
-        <v>2813.123062825936</v>
+        <v>2756.680033706447</v>
       </c>
       <c r="T41" t="n">
-        <v>2813.123062825936</v>
+        <v>2361.048132970524</v>
       </c>
       <c r="U41" t="n">
-        <v>2593.002440524087</v>
+        <v>1902.238742517382</v>
       </c>
       <c r="V41" t="n">
-        <v>2153.758981769719</v>
+        <v>1462.995283763014</v>
       </c>
       <c r="W41" t="n">
-        <v>1705.906985829368</v>
+        <v>1015.143287822663</v>
       </c>
       <c r="X41" t="n">
-        <v>1705.906985829368</v>
+        <v>613.8485065492615</v>
       </c>
       <c r="Y41" t="n">
-        <v>1386.394427563907</v>
+        <v>294.3359482838005</v>
       </c>
     </row>
     <row r="42">
@@ -7457,22 +7457,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>972.804795813948</v>
+        <v>556.0938206631142</v>
       </c>
       <c r="C42" t="n">
-        <v>805.0271064750395</v>
+        <v>388.3161313242059</v>
       </c>
       <c r="D42" t="n">
-        <v>650.5445944571582</v>
+        <v>233.8336193063244</v>
       </c>
       <c r="E42" t="n">
-        <v>501.3808598895696</v>
+        <v>84.6698847387359</v>
       </c>
       <c r="F42" t="n">
-        <v>355.2836454068657</v>
+        <v>84.6698847387359</v>
       </c>
       <c r="G42" t="n">
-        <v>223.2235081593633</v>
+        <v>84.6698847387359</v>
       </c>
       <c r="H42" t="n">
         <v>84.6698847387359</v>
@@ -7487,46 +7487,46 @@
         <v>761.5693362696824</v>
       </c>
       <c r="L42" t="n">
-        <v>1042.738970404614</v>
+        <v>1225.969797864882</v>
       </c>
       <c r="M42" t="n">
-        <v>1321.869512147473</v>
+        <v>1505.100339607742</v>
       </c>
       <c r="N42" t="n">
-        <v>1648.199796755041</v>
+        <v>1831.43062421531</v>
       </c>
       <c r="O42" t="n">
-        <v>2080.29224843876</v>
+        <v>2263.523075899029</v>
       </c>
       <c r="P42" t="n">
-        <v>2385.871592908267</v>
+        <v>2437.452290867012</v>
       </c>
       <c r="Q42" t="n">
-        <v>2407.573120468692</v>
+        <v>2459.153818427438</v>
       </c>
       <c r="R42" t="n">
-        <v>2251.996598330625</v>
+        <v>2103.321699950287</v>
       </c>
       <c r="S42" t="n">
-        <v>2251.996598330625</v>
+        <v>1829.014629278963</v>
       </c>
       <c r="T42" t="n">
-        <v>2039.514007201823</v>
+        <v>1616.532038150161</v>
       </c>
       <c r="U42" t="n">
-        <v>1832.230815524867</v>
+        <v>1409.248846473204</v>
       </c>
       <c r="V42" t="n">
-        <v>1610.502868866766</v>
+        <v>1187.520899815103</v>
       </c>
       <c r="W42" t="n">
-        <v>1370.732017442696</v>
+        <v>1181.155122539729</v>
       </c>
       <c r="X42" t="n">
-        <v>1370.732017442696</v>
+        <v>954.0210422918627</v>
       </c>
       <c r="Y42" t="n">
-        <v>1164.276065153672</v>
+        <v>747.5650900028381</v>
       </c>
     </row>
     <row r="43">
@@ -7536,19 +7536,19 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>146.9816150940896</v>
+        <v>96.43224858749356</v>
       </c>
       <c r="C43" t="n">
-        <v>146.9816150940896</v>
+        <v>96.43224858749356</v>
       </c>
       <c r="D43" t="n">
-        <v>146.9816150940896</v>
+        <v>96.43224858749356</v>
       </c>
       <c r="E43" t="n">
-        <v>146.9816150940896</v>
+        <v>96.43224858749356</v>
       </c>
       <c r="F43" t="n">
-        <v>146.9816150940896</v>
+        <v>96.43224858749356</v>
       </c>
       <c r="G43" t="n">
         <v>96.43224858749356</v>
@@ -7557,55 +7557,55 @@
         <v>62.32</v>
       </c>
       <c r="I43" t="n">
-        <v>80.50287893608291</v>
+        <v>62.32</v>
       </c>
       <c r="J43" t="n">
-        <v>238.6366195885342</v>
+        <v>103.9095272231297</v>
       </c>
       <c r="K43" t="n">
-        <v>238.6366195885342</v>
+        <v>103.9095272231297</v>
       </c>
       <c r="L43" t="n">
-        <v>238.6366195885342</v>
+        <v>103.9095272231297</v>
       </c>
       <c r="M43" t="n">
-        <v>238.6366195885342</v>
+        <v>103.9095272231297</v>
       </c>
       <c r="N43" t="n">
-        <v>238.6366195885342</v>
+        <v>103.9095272231297</v>
       </c>
       <c r="O43" t="n">
-        <v>238.6366195885342</v>
+        <v>103.9095272231297</v>
       </c>
       <c r="P43" t="n">
-        <v>238.6366195885342</v>
+        <v>103.9095272231297</v>
       </c>
       <c r="Q43" t="n">
-        <v>238.6366195885342</v>
+        <v>103.9095272231297</v>
       </c>
       <c r="R43" t="n">
-        <v>178.6713220018771</v>
+        <v>103.9095272231297</v>
       </c>
       <c r="S43" t="n">
-        <v>178.6713220018771</v>
+        <v>103.9095272231297</v>
       </c>
       <c r="T43" t="n">
-        <v>178.6713220018771</v>
+        <v>88.73319741882901</v>
       </c>
       <c r="U43" t="n">
-        <v>178.6713220018771</v>
+        <v>132.3343900571157</v>
       </c>
       <c r="V43" t="n">
-        <v>178.6713220018771</v>
+        <v>128.1219554952811</v>
       </c>
       <c r="W43" t="n">
-        <v>146.9816150940896</v>
+        <v>96.43224858749356</v>
       </c>
       <c r="X43" t="n">
-        <v>146.9816150940896</v>
+        <v>96.43224858749356</v>
       </c>
       <c r="Y43" t="n">
-        <v>146.9816150940896</v>
+        <v>96.43224858749356</v>
       </c>
     </row>
     <row r="44">
@@ -7615,46 +7615,46 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1276.695436194001</v>
+        <v>345.4424731060063</v>
       </c>
       <c r="C44" t="n">
-        <v>1276.695436194001</v>
+        <v>97.75551483099457</v>
       </c>
       <c r="D44" t="n">
-        <v>978.373056658799</v>
+        <v>97.75551483099457</v>
       </c>
       <c r="E44" t="n">
-        <v>686.0869055407499</v>
+        <v>97.75551483099457</v>
       </c>
       <c r="F44" t="n">
-        <v>649.9634656470138</v>
+        <v>97.75551483099457</v>
       </c>
       <c r="G44" t="n">
-        <v>358.2893522257853</v>
+        <v>97.75551483099457</v>
       </c>
       <c r="H44" t="n">
-        <v>62.32</v>
+        <v>97.75551483099457</v>
       </c>
       <c r="I44" t="n">
         <v>62.32</v>
       </c>
       <c r="J44" t="n">
-        <v>453.6291130376557</v>
+        <v>72.41539009576594</v>
       </c>
       <c r="K44" t="n">
-        <v>453.6291130376557</v>
+        <v>782.1217564436344</v>
       </c>
       <c r="L44" t="n">
-        <v>624.132076217999</v>
+        <v>1553.331756443634</v>
       </c>
       <c r="M44" t="n">
-        <v>1134.980904946934</v>
+        <v>2064.180585172569</v>
       </c>
       <c r="N44" t="n">
-        <v>1134.980904946934</v>
+        <v>2677.400904947332</v>
       </c>
       <c r="O44" t="n">
-        <v>1906.190904947133</v>
+        <v>2677.400904947332</v>
       </c>
       <c r="P44" t="n">
         <v>2677.400904947332</v>
@@ -7663,28 +7663,28 @@
         <v>3116</v>
       </c>
       <c r="R44" t="n">
-        <v>3116</v>
+        <v>2978.74889007243</v>
       </c>
       <c r="S44" t="n">
-        <v>3116</v>
+        <v>2595.063872090285</v>
       </c>
       <c r="T44" t="n">
-        <v>3116</v>
+        <v>2118.623890546281</v>
       </c>
       <c r="U44" t="n">
-        <v>2576.382528738777</v>
+        <v>2118.623890546281</v>
       </c>
       <c r="V44" t="n">
-        <v>2576.382528738777</v>
+        <v>1598.572350983833</v>
       </c>
       <c r="W44" t="n">
-        <v>2047.722451990345</v>
+        <v>1598.572350983833</v>
       </c>
       <c r="X44" t="n">
-        <v>2047.722451990345</v>
+        <v>1116.469488902351</v>
       </c>
       <c r="Y44" t="n">
-        <v>1647.401812916803</v>
+        <v>716.1488498288088</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>989.036396404204</v>
+        <v>924.3895429982276</v>
       </c>
       <c r="C45" t="n">
-        <v>740.4506262572148</v>
+        <v>675.8037728512384</v>
       </c>
       <c r="D45" t="n">
-        <v>505.1600334312525</v>
+        <v>605.2514788931846</v>
       </c>
       <c r="E45" t="n">
-        <v>275.1882180555832</v>
+        <v>605.2514788931846</v>
       </c>
       <c r="F45" t="n">
-        <v>275.1882180555832</v>
+        <v>378.3461836023999</v>
       </c>
       <c r="G45" t="n">
-        <v>62.32</v>
+        <v>165.4779655468167</v>
       </c>
       <c r="H45" t="n">
-        <v>62.32</v>
+        <v>165.4779655468167</v>
       </c>
       <c r="I45" t="n">
         <v>62.32</v>
       </c>
       <c r="J45" t="n">
-        <v>300.126520175299</v>
+        <v>266.2475390269107</v>
       </c>
       <c r="K45" t="n">
-        <v>603.1693362696824</v>
+        <v>569.2903551212941</v>
       </c>
       <c r="L45" t="n">
-        <v>988.3697978648825</v>
+        <v>954.4908167164942</v>
       </c>
       <c r="M45" t="n">
-        <v>1074.450339607742</v>
+        <v>1154.421358459354</v>
       </c>
       <c r="N45" t="n">
-        <v>1321.58062421531</v>
+        <v>1401.551643066922</v>
       </c>
       <c r="O45" t="n">
-        <v>1616.474019295255</v>
+        <v>1754.444094750641</v>
       </c>
       <c r="P45" t="n">
-        <v>1842.853363764762</v>
+        <v>1866.973439220147</v>
       </c>
       <c r="Q45" t="n">
-        <v>1842.853363764762</v>
+        <v>1808.307514886329</v>
       </c>
       <c r="R45" t="n">
-        <v>1842.853363764762</v>
+        <v>1808.307514886329</v>
       </c>
       <c r="S45" t="n">
-        <v>1842.853363764762</v>
+        <v>1808.307514886329</v>
       </c>
       <c r="T45" t="n">
-        <v>1842.853363764762</v>
+        <v>1515.016842949447</v>
       </c>
       <c r="U45" t="n">
-        <v>1554.762091279725</v>
+        <v>1226.92557046441</v>
       </c>
       <c r="V45" t="n">
-        <v>1554.762091279725</v>
+        <v>924.3895429982276</v>
       </c>
       <c r="W45" t="n">
-        <v>1554.762091279725</v>
+        <v>924.3895429982276</v>
       </c>
       <c r="X45" t="n">
-        <v>1276.300429501309</v>
+        <v>924.3895429982276</v>
       </c>
       <c r="Y45" t="n">
-        <v>989.036396404204</v>
+        <v>924.3895429982276</v>
       </c>
     </row>
     <row r="46">
@@ -7797,37 +7797,37 @@
         <v>62.32</v>
       </c>
       <c r="J46" t="n">
-        <v>141.2537406524513</v>
+        <v>98.64160734793731</v>
       </c>
       <c r="K46" t="n">
-        <v>141.2537406524513</v>
+        <v>98.64160734793731</v>
       </c>
       <c r="L46" t="n">
-        <v>141.2537406524513</v>
+        <v>98.64160734793731</v>
       </c>
       <c r="M46" t="n">
-        <v>141.2537406524513</v>
+        <v>98.64160734793731</v>
       </c>
       <c r="N46" t="n">
-        <v>141.2537406524513</v>
+        <v>98.64160734793731</v>
       </c>
       <c r="O46" t="n">
-        <v>141.2537406524513</v>
+        <v>98.64160734793731</v>
       </c>
       <c r="P46" t="n">
-        <v>141.2537406524513</v>
+        <v>98.64160734793731</v>
       </c>
       <c r="Q46" t="n">
-        <v>141.2537406524513</v>
+        <v>98.64160734793731</v>
       </c>
       <c r="R46" t="n">
-        <v>141.2537406524513</v>
+        <v>98.64160734793731</v>
       </c>
       <c r="S46" t="n">
-        <v>141.2537406524513</v>
+        <v>98.64160734793731</v>
       </c>
       <c r="T46" t="n">
-        <v>62.32</v>
+        <v>98.64160734793731</v>
       </c>
       <c r="U46" t="n">
         <v>62.32</v>
@@ -7964,13 +7964,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>51.26150624509023</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K2" t="n">
-        <v>16.21850000000013</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>51.07361380696631</v>
+        <v>115.0597724079888</v>
       </c>
       <c r="M2" t="n">
         <v>1060.271045550332</v>
@@ -7985,7 +7985,7 @@
         <v>815.2870600406815</v>
       </c>
       <c r="Q2" t="n">
-        <v>615.8520732695737</v>
+        <v>189.0411843274853</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8204,7 +8204,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K5" t="n">
-        <v>716.8751175230994</v>
+        <v>503.2488834658994</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -8219,10 +8219,10 @@
         <v>885.2478695740924</v>
       </c>
       <c r="P5" t="n">
-        <v>213.4717149255709</v>
+        <v>0.2870600406826043</v>
       </c>
       <c r="Q5" t="n">
-        <v>189.0411843274853</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8441,7 +8441,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K8" t="n">
-        <v>716.8751175230994</v>
+        <v>204.5448614145976</v>
       </c>
       <c r="L8" t="n">
         <v>815</v>
@@ -8453,10 +8453,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O8" t="n">
-        <v>38.25716987680642</v>
+        <v>885.2478695740924</v>
       </c>
       <c r="P8" t="n">
-        <v>334.6604435887855</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>615.8520732695737</v>
@@ -8675,28 +8675,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>430.3047365861567</v>
+        <v>151.7858245236418</v>
       </c>
       <c r="K11" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="M11" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N11" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O11" t="n">
-        <v>750.7672643616811</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P11" t="n">
-        <v>815.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q11" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8912,25 +8912,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>100.2385957926983</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K14" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L14" t="n">
-        <v>815</v>
+        <v>559.7722072206399</v>
       </c>
       <c r="M14" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N14" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O14" t="n">
         <v>885.2478695740924</v>
       </c>
       <c r="P14" t="n">
-        <v>815.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q14" t="n">
         <v>172.8226843274854</v>
@@ -9149,28 +9149,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K17" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>814.9999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N17" t="n">
-        <v>962.1828172763766</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O17" t="n">
-        <v>885.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P17" t="n">
-        <v>815.2870600406815</v>
+        <v>117.0298783192331</v>
       </c>
       <c r="Q17" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,28 +9386,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L20" t="n">
-        <v>814.9999999999999</v>
+        <v>783.9249412985259</v>
       </c>
       <c r="M20" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N20" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O20" t="n">
-        <v>885.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2870600406814136</v>
+        <v>815.2870600406815</v>
       </c>
       <c r="Q20" t="n">
-        <v>433.6038094561404</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9629,22 +9629,22 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L23" t="n">
-        <v>815</v>
+        <v>164.5104768795734</v>
       </c>
       <c r="M23" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N23" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O23" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P23" t="n">
-        <v>341.1826123971189</v>
+        <v>815.2870600406815</v>
       </c>
       <c r="Q23" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9863,22 +9863,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L26" t="n">
-        <v>774.8401398571921</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N26" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O26" t="n">
-        <v>849.2478695741188</v>
+        <v>747.6273563271385</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2870600406814136</v>
+        <v>779.2870600407069</v>
       </c>
       <c r="Q26" t="n">
         <v>172.8226843274854</v>
@@ -10100,25 +10100,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>688.2341332420267</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>779</v>
       </c>
       <c r="M29" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N29" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O29" t="n">
-        <v>849.2478695741281</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P29" t="n">
-        <v>779.2870600407172</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q29" t="n">
-        <v>615.8520732695737</v>
+        <v>230.7877066616041</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10334,25 +10334,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L32" t="n">
-        <v>779</v>
+        <v>751.3303335113429</v>
       </c>
       <c r="M32" t="n">
         <v>544.2621276423173</v>
       </c>
       <c r="N32" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O32" t="n">
-        <v>597.4254690075953</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P32" t="n">
-        <v>0.2870600406814136</v>
+        <v>779.2870600407272</v>
       </c>
       <c r="Q32" t="n">
         <v>615.8520732695737</v>
@@ -10574,22 +10574,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L35" t="n">
-        <v>731.1613784763163</v>
+        <v>678.3508045453917</v>
       </c>
       <c r="M35" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N35" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O35" t="n">
-        <v>630.906866655333</v>
+        <v>849.2478695741627</v>
       </c>
       <c r="P35" t="n">
-        <v>779.2870600407481</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q35" t="n">
         <v>172.8226843274854</v>
@@ -10808,25 +10808,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>340.5101876207173</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L38" t="n">
-        <v>779</v>
+        <v>394.9069511844207</v>
       </c>
       <c r="M38" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N38" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O38" t="n">
-        <v>849.247869574179</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P38" t="n">
-        <v>779.2870600407681</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q38" t="n">
         <v>615.8520732695737</v>
@@ -11051,7 +11051,7 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>779</v>
       </c>
       <c r="M41" t="n">
         <v>1060.271045550332</v>
@@ -11063,10 +11063,10 @@
         <v>70.24786957409245</v>
       </c>
       <c r="P41" t="n">
-        <v>394.2226934327118</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q41" t="n">
-        <v>615.8520732695737</v>
+        <v>230.7877066616041</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,25 +11282,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>430.3047365861567</v>
+        <v>45.24036997818725</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L44" t="n">
-        <v>172.2252153336802</v>
+        <v>779</v>
       </c>
       <c r="M44" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N44" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O44" t="n">
-        <v>849.2478695742936</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P44" t="n">
-        <v>779.2870600408827</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q44" t="n">
         <v>615.8520732695737</v>
@@ -23226,7 +23226,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>224.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -23241,7 +23241,7 @@
         <v>178.7573722870162</v>
       </c>
       <c r="H11" t="n">
-        <v>15.94353859798946</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -23271,10 +23271,10 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>25.87859882829446</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>214.5395180126893</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -23384,22 +23384,22 @@
         <v>62.11380033707866</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>47.72524664804467</v>
       </c>
       <c r="D13" t="n">
-        <v>46.45584847384474</v>
+        <v>60.53621805555548</v>
       </c>
       <c r="E13" t="n">
         <v>55.98090483695654</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>49.38285596774193</v>
       </c>
       <c r="G13" t="n">
         <v>20.04387284153003</v>
       </c>
       <c r="H13" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>63.52077380114304</v>
       </c>
       <c r="L13" t="n">
         <v>198.5476281577792</v>
@@ -23423,10 +23423,10 @@
         <v>415.445564079015</v>
       </c>
       <c r="P13" t="n">
-        <v>292.6092177367716</v>
+        <v>462.4478973282775</v>
       </c>
       <c r="Q13" t="n">
-        <v>500.839266425598</v>
+        <v>160.0624669370704</v>
       </c>
       <c r="R13" t="n">
         <v>501.6021279811511</v>
@@ -23618,16 +23618,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>8.113800337078658</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>6.53621805555548</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1.98090483695654</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -23648,7 +23648,7 @@
         <v>9.520773801143037</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>144.5476281577792</v>
       </c>
       <c r="M16" t="n">
         <v>241.6316114025499</v>
@@ -23657,13 +23657,13 @@
         <v>292.1850752716849</v>
       </c>
       <c r="O16" t="n">
-        <v>153.2964698621488</v>
+        <v>361.445564079015</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>69.04626797189968</v>
       </c>
       <c r="Q16" t="n">
-        <v>446.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>447.6021279811511</v>
@@ -23687,7 +23687,7 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>8.465352849462363</v>
       </c>
     </row>
     <row r="17">
@@ -23861,7 +23861,7 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>6.53621805555548</v>
       </c>
       <c r="E19" t="n">
         <v>1.98090483695654</v>
@@ -23891,16 +23891,16 @@
         <v>241.6316114025499</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>292.1850752716849</v>
       </c>
       <c r="O19" t="n">
         <v>361.445564079015</v>
       </c>
       <c r="P19" t="n">
-        <v>368.5304228546933</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q19" t="n">
-        <v>446.839266425598</v>
+        <v>108.2004986247733</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -24128,22 +24128,22 @@
         <v>241.6316114025499</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>292.1850752716849</v>
       </c>
       <c r="O22" t="n">
-        <v>359.211120599857</v>
+        <v>361.445564079015</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>446.839266425598</v>
+        <v>69.04626797189968</v>
       </c>
       <c r="R22" t="n">
         <v>447.6021279811511</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>83.37347970285543</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24335,10 +24335,10 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>6.53621805555548</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1.98090483695654</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -24356,7 +24356,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>9.520773801143037</v>
       </c>
       <c r="L25" t="n">
         <v>144.5476281577792</v>
@@ -24371,13 +24371,13 @@
         <v>361.445564079015</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q25" t="n">
-        <v>446.839266425598</v>
+        <v>108.2004986247733</v>
       </c>
       <c r="R25" t="n">
-        <v>87.8470262211078</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>83.37347970285543</v>
@@ -24411,22 +24411,22 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>11.77810239760592</v>
       </c>
       <c r="D26" t="n">
         <v>185.3391557398498</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24468,13 +24468,13 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>365.5162182423623</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>367.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -24584,7 +24584,7 @@
         <v>20.04387284153003</v>
       </c>
       <c r="H28" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -24608,13 +24608,13 @@
         <v>415.445564079015</v>
       </c>
       <c r="P28" t="n">
-        <v>116.5271618994215</v>
+        <v>462.4478973282775</v>
       </c>
       <c r="Q28" t="n">
         <v>500.839266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>501.6021279811511</v>
+        <v>160.8253284926234</v>
       </c>
       <c r="S28" t="n">
         <v>137.3734797028554</v>
@@ -24629,7 +24629,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>22.44364543010755</v>
@@ -24645,22 +24645,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>230.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>198.4745782429939</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>153.3632896068686</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>23.66336847770674</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>152.7573722870162</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -24705,7 +24705,7 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>36.94186297620479</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
@@ -24714,7 +24714,7 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>260.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -24839,13 +24839,13 @@
         <v>269.6316114025499</v>
       </c>
       <c r="N31" t="n">
-        <v>320.1850752716849</v>
+        <v>267.2066560971279</v>
       </c>
       <c r="O31" t="n">
         <v>389.445564079015</v>
       </c>
       <c r="P31" t="n">
-        <v>383.4694781537204</v>
+        <v>436.4478973282775</v>
       </c>
       <c r="Q31" t="n">
         <v>474.839266425598</v>
@@ -24888,7 +24888,7 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>10.2586086145855</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -24933,7 +24933,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>10.25860861458523</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
@@ -25070,13 +25070,13 @@
         <v>0.5207738011430365</v>
       </c>
       <c r="L34" t="n">
-        <v>135.5476281577792</v>
+        <v>109.8523433141331</v>
       </c>
       <c r="M34" t="n">
-        <v>232.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>253.8858498822575</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -25085,13 +25085,13 @@
         <v>399.4478973282775</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>437.839266425598</v>
       </c>
       <c r="R34" t="n">
         <v>438.6021279811511</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>74.37347970285543</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -25170,7 +25170,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>10.25860861458523</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
@@ -25179,7 +25179,7 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>10.2586086145858</v>
       </c>
       <c r="W35" t="n">
         <v>0</v>
@@ -25310,22 +25310,22 @@
         <v>135.5476281577792</v>
       </c>
       <c r="M37" t="n">
-        <v>90.56753721294643</v>
+        <v>232.6316114025499</v>
       </c>
       <c r="N37" t="n">
         <v>283.1850752716849</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>352.445564079015</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>437.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>438.6021279811511</v>
+        <v>381.9317561381307</v>
       </c>
       <c r="S37" t="n">
         <v>74.37347970285543</v>
@@ -25407,10 +25407,10 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>10.25860861458523</v>
       </c>
       <c r="T38" t="n">
-        <v>10.25860861422314</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -25544,28 +25544,28 @@
         <v>0.5207738011430365</v>
       </c>
       <c r="L40" t="n">
-        <v>135.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>232.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>283.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>352.445564079015</v>
+        <v>109.8523433141332</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>399.4478973282775</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>437.839266425598</v>
       </c>
       <c r="R40" t="n">
         <v>438.6021279811511</v>
       </c>
       <c r="S40" t="n">
-        <v>17.70310785983509</v>
+        <v>74.37347970285543</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -25593,25 +25593,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>286.9993129555745</v>
+        <v>57.30352415461198</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>254.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>215.3391557398498</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>209.3632896068686</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>209.8896287080119</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>208.7573722870162</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>213.0096587035274</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25641,16 +25641,16 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>55.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>391.6755817285639</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>236.3018804697793</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -25659,7 +25659,7 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>397.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -25684,13 +25684,13 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>144.6362423378769</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>130.7395358750273</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>137.1680871864211</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -25720,10 +25720,10 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>198.2530403756925</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>271.5639999646113</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
@@ -25735,10 +25735,10 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>231.0710234072082</v>
       </c>
       <c r="X42" t="n">
-        <v>224.8627394453875</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
@@ -25766,7 +25766,7 @@
         <v>79.38285596774193</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>50.04387284153003</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -25799,19 +25799,19 @@
         <v>530.839266425598</v>
       </c>
       <c r="R43" t="n">
-        <v>472.2364833703605</v>
+        <v>531.6021279811511</v>
       </c>
       <c r="S43" t="n">
         <v>167.3734797028554</v>
       </c>
       <c r="T43" t="n">
-        <v>15.02456650625771</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>4.170310216216194</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
         <v>0</v>
@@ -25833,25 +25833,25 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>334.4745782429939</v>
+        <v>89.26448955073232</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>295.3391557398498</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>289.3632896068686</v>
       </c>
       <c r="F44" t="n">
-        <v>254.1274232132131</v>
+        <v>289.8896287080119</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>288.7573722870162</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>293.0096587035274</v>
       </c>
       <c r="I44" t="n">
-        <v>35.08115968268461</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -25878,25 +25878,25 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>135.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>379.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>471.6755817285639</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>534.2212965486107</v>
       </c>
       <c r="V44" t="n">
-        <v>514.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>523.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>477.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -25915,13 +25915,13 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>163.0909158792294</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>227.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>224.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -25930,7 +25930,7 @@
         <v>217.1680871864211</v>
       </c>
       <c r="I45" t="n">
-        <v>102.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25954,7 +25954,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>58.07926509047959</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>432.2737972923793</v>
@@ -25963,22 +25963,22 @@
         <v>351.5639999646113</v>
       </c>
       <c r="T45" t="n">
-        <v>290.3577652175138</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>299.5106671915202</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
         <v>317.3731429098285</v>
       </c>
       <c r="X45" t="n">
-        <v>29.18569428475627</v>
+        <v>304.8627394453875</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>284.3913927661343</v>
       </c>
     </row>
     <row r="46">
@@ -26042,10 +26042,10 @@
         <v>247.3734797028554</v>
       </c>
       <c r="T46" t="n">
-        <v>16.8801632603309</v>
+        <v>95.02456650625771</v>
       </c>
       <c r="U46" t="n">
-        <v>35.95839127445794</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
         <v>84.17031021621619</v>
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8852457.517993128</v>
+        <v>8852457.51799313</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9739516.179771949</v>
+        <v>9739516.179771947</v>
       </c>
     </row>
     <row r="13">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11513598.7107263</v>
+        <v>11513598.71072628</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12261555.98415491</v>
+        <v>12261555.98415489</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12847328.05747462</v>
+        <v>12847328.0574746</v>
       </c>
     </row>
   </sheetData>
@@ -26275,7 +26275,7 @@
         <v>1290861.46634091</v>
       </c>
       <c r="D2" t="n">
-        <v>1290861.466340909</v>
+        <v>1290861.46634091</v>
       </c>
       <c r="E2" t="n">
         <v>1154496.382945596</v>
@@ -26284,7 +26284,7 @@
         <v>1249670.02575151</v>
       </c>
       <c r="G2" t="n">
-        <v>1249670.02575151</v>
+        <v>1249670.025751511</v>
       </c>
       <c r="H2" t="n">
         <v>1249670.02575151</v>
@@ -26293,25 +26293,25 @@
         <v>1249670.02575151</v>
       </c>
       <c r="J2" t="n">
-        <v>1143097.541953596</v>
+        <v>1143097.541953597</v>
       </c>
       <c r="K2" t="n">
         <v>1190166.901974092</v>
       </c>
       <c r="L2" t="n">
-        <v>1254092.823605639</v>
+        <v>1254092.823605638</v>
       </c>
       <c r="M2" t="n">
         <v>1254092.823605638</v>
       </c>
       <c r="N2" t="n">
-        <v>1254092.823605667</v>
+        <v>1254092.823605638</v>
       </c>
       <c r="O2" t="n">
         <v>1057481.429618647</v>
       </c>
       <c r="P2" t="n">
-        <v>828160.5174519987</v>
+        <v>828160.5174519988</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>556518.3877202002</v>
+        <v>551678.2037907119</v>
       </c>
       <c r="C4" t="n">
-        <v>554765.5452197595</v>
+        <v>549925.361290271</v>
       </c>
       <c r="D4" t="n">
-        <v>553010.324879062</v>
+        <v>548170.1409495736</v>
       </c>
       <c r="E4" t="n">
-        <v>474768.9161162032</v>
+        <v>469977.895301786</v>
       </c>
       <c r="F4" t="n">
-        <v>525348.7383112749</v>
+        <v>520557.7174968576</v>
       </c>
       <c r="G4" t="n">
-        <v>523678.7566207297</v>
+        <v>518887.7358063125</v>
       </c>
       <c r="H4" t="n">
-        <v>522006.457090894</v>
+        <v>517215.4362764768</v>
       </c>
       <c r="I4" t="n">
-        <v>520331.8230037717</v>
+        <v>515540.8021893546</v>
       </c>
       <c r="J4" t="n">
-        <v>464813.3679854202</v>
+        <v>460130.3405348169</v>
       </c>
       <c r="K4" t="n">
-        <v>488548.683349176</v>
+        <v>483865.6558985728</v>
       </c>
       <c r="L4" t="n">
-        <v>521101.9613805412</v>
+        <v>516418.1980532586</v>
       </c>
       <c r="M4" t="n">
-        <v>519382.0000515243</v>
+        <v>514698.2367242419</v>
       </c>
       <c r="N4" t="n">
-        <v>517659.5657041428</v>
+        <v>512975.8023768382</v>
       </c>
       <c r="O4" t="n">
-        <v>411958.788736175</v>
+        <v>407275.7612855717</v>
       </c>
       <c r="P4" t="n">
-        <v>289436.0308461937</v>
+        <v>284753.0033955905</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>364283.4786207095</v>
+        <v>369123.662550198</v>
       </c>
       <c r="C6" t="n">
-        <v>652916.3211211503</v>
+        <v>657756.5050506387</v>
       </c>
       <c r="D6" t="n">
-        <v>654671.541461847</v>
+        <v>659511.7253913366</v>
       </c>
       <c r="E6" t="n">
-        <v>431259.941829393</v>
+        <v>436050.9626438104</v>
       </c>
       <c r="F6" t="n">
-        <v>608114.0364402352</v>
+        <v>612905.0572546527</v>
       </c>
       <c r="G6" t="n">
-        <v>652984.0181307807</v>
+        <v>657775.0389451981</v>
       </c>
       <c r="H6" t="n">
-        <v>654656.3176606164</v>
+        <v>659447.3384750335</v>
       </c>
       <c r="I6" t="n">
-        <v>656330.9517477386</v>
+        <v>661121.9725621558</v>
       </c>
       <c r="J6" t="n">
-        <v>200997.4489681761</v>
+        <v>205680.4764187796</v>
       </c>
       <c r="K6" t="n">
-        <v>569153.6996249156</v>
+        <v>573836.727075519</v>
       </c>
       <c r="L6" t="n">
-        <v>631815.7902250974</v>
+        <v>636499.5535523795</v>
       </c>
       <c r="M6" t="n">
-        <v>663135.7515541135</v>
+        <v>667819.5148813961</v>
       </c>
       <c r="N6" t="n">
-        <v>664858.1859015243</v>
+        <v>669541.9492287998</v>
       </c>
       <c r="O6" t="n">
-        <v>519365.9858824718</v>
+        <v>524049.0133330749</v>
       </c>
       <c r="P6" t="n">
-        <v>481693.3516058049</v>
+        <v>486376.3790564083</v>
       </c>
     </row>
   </sheetData>
@@ -26987,13 +26987,13 @@
         <v>54</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="n">
         <v>171</v>
@@ -27005,10 +27005,10 @@
         <v>37</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>78</v>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
@@ -27445,10 +27445,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G2" t="n">
-        <v>303.5095671255644</v>
+        <v>400</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -27484,10 +27484,10 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>400</v>
+        <v>303.5095671255646</v>
       </c>
       <c r="T2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>400</v>
@@ -27521,13 +27521,13 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>332.1680871864211</v>
@@ -27566,10 +27566,10 @@
         <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>54.98988304493378</v>
+        <v>400</v>
       </c>
       <c r="U3" t="n">
-        <v>400</v>
+        <v>383.765273803997</v>
       </c>
       <c r="V3" t="n">
         <v>400</v>
@@ -27597,28 +27597,28 @@
         <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>351.748915710332</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
         <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>274.3828559677419</v>
+        <v>301.0451253455172</v>
       </c>
       <c r="G4" t="n">
         <v>400</v>
       </c>
       <c r="H4" t="n">
-        <v>228.7711261016186</v>
+        <v>400</v>
       </c>
       <c r="I4" t="n">
-        <v>176.6334556201183</v>
+        <v>400</v>
       </c>
       <c r="J4" t="n">
         <v>400</v>
       </c>
       <c r="K4" t="n">
-        <v>288.520773801143</v>
+        <v>400</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27642,22 +27642,22 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T4" t="n">
-        <v>400</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U4" t="n">
         <v>150.9583912744579</v>
       </c>
       <c r="V4" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
         <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
         <v>287.4653528494624</v>
@@ -27679,55 +27679,55 @@
         <v>400</v>
       </c>
       <c r="E5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>400</v>
       </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>303.5095671255646</v>
+      </c>
+      <c r="T5" t="n">
         <v>400</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>150.0811596826846</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>153.4284074428799</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="V5" t="n">
         <v>400</v>
@@ -27749,13 +27749,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>274.7686191606065</v>
+        <v>290.2120625142799</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
@@ -27812,7 +27812,7 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>400</v>
@@ -27828,7 +27828,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
         <v>400</v>
@@ -27843,16 +27843,16 @@
         <v>400</v>
       </c>
       <c r="G7" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H7" t="n">
-        <v>228.7711261016186</v>
+        <v>400</v>
       </c>
       <c r="I7" t="n">
         <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>279.8210068813129</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K7" t="n">
         <v>400</v>
@@ -27882,22 +27882,22 @@
         <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>210.0245665062577</v>
+        <v>325.6395755681847</v>
       </c>
       <c r="U7" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V7" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
         <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8">
@@ -27913,20 +27913,20 @@
         <v>400</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E8" t="n">
         <v>400</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
         <v>400</v>
       </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -27955,16 +27955,16 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>400</v>
+        <v>52.63096829727021</v>
       </c>
       <c r="V8" t="n">
         <v>400</v>
@@ -27976,7 +27976,7 @@
         <v>400</v>
       </c>
       <c r="Y8" t="n">
-        <v>303.5095671255647</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
@@ -27992,16 +27992,16 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>229.2396976182912</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>323.4015161418739</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>332.1680871864211</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
@@ -28055,7 +28055,7 @@
         <v>400</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="10">
@@ -28065,13 +28065,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C10" t="n">
-        <v>272.7252466480447</v>
+        <v>347.4029453491425</v>
       </c>
       <c r="D10" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
         <v>280.9809048369565</v>
@@ -28086,10 +28086,10 @@
         <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>176.6334556201183</v>
+        <v>400</v>
       </c>
       <c r="J10" t="n">
-        <v>400</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K10" t="n">
         <v>400</v>
@@ -28116,25 +28116,25 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T10" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U10" t="n">
-        <v>150.9583912744579</v>
+        <v>400</v>
       </c>
       <c r="V10" t="n">
         <v>400</v>
       </c>
       <c r="W10" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
-        <v>369.660980270073</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28247,10 +28247,10 @@
         <v>225</v>
       </c>
       <c r="J12" t="n">
+        <v>19.11687125883931</v>
+      </c>
+      <c r="K12" t="n">
         <v>225</v>
-      </c>
-      <c r="K12" t="n">
-        <v>19.1168712588393</v>
       </c>
       <c r="L12" t="n">
         <v>225</v>
@@ -28402,7 +28402,7 @@
         <v>279</v>
       </c>
       <c r="I14" t="n">
-        <v>146.6309682972706</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28429,7 +28429,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>250.8785988282945</v>
+        <v>247.42840744288</v>
       </c>
       <c r="S14" t="n">
         <v>279</v>
@@ -28487,19 +28487,19 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>44.46493928527485</v>
       </c>
       <c r="M15" t="n">
         <v>279</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="O15" t="n">
-        <v>44.46493928527505</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -28630,7 +28630,7 @@
         <v>279</v>
       </c>
       <c r="F17" t="n">
-        <v>279</v>
+        <v>275.549808614586</v>
       </c>
       <c r="G17" t="n">
         <v>279</v>
@@ -28669,7 +28669,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S17" t="n">
-        <v>275.5498086145856</v>
+        <v>279</v>
       </c>
       <c r="T17" t="n">
         <v>279</v>
@@ -28718,10 +28718,10 @@
         <v>279</v>
       </c>
       <c r="I18" t="n">
-        <v>261.5913251766233</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="K18" t="n">
         <v>279</v>
@@ -28733,13 +28733,13 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>44.46493928527515</v>
       </c>
       <c r="Q18" t="n">
         <v>173.0792650904796</v>
@@ -28955,31 +28955,31 @@
         <v>279</v>
       </c>
       <c r="I21" t="n">
-        <v>217.1263858913485</v>
+        <v>279</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>155.6705902671029</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
         <v>279</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>44.46493928527485</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
       <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>279</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>173.0792650904796</v>
       </c>
       <c r="R21" t="n">
         <v>279</v>
@@ -29110,7 +29110,7 @@
         <v>279</v>
       </c>
       <c r="H23" t="n">
-        <v>279</v>
+        <v>275.549808614586</v>
       </c>
       <c r="I23" t="n">
         <v>150.0811596826846</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>247.42840744288</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S23" t="n">
         <v>279</v>
@@ -29192,16 +29192,16 @@
         <v>279</v>
       </c>
       <c r="I24" t="n">
-        <v>217.1263858913485</v>
+        <v>279</v>
       </c>
       <c r="J24" t="n">
-        <v>44.46493928527465</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -29210,13 +29210,13 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>155.6705902671029</v>
       </c>
       <c r="P24" t="n">
         <v>279</v>
       </c>
       <c r="Q24" t="n">
-        <v>173.0792650904796</v>
+        <v>279</v>
       </c>
       <c r="R24" t="n">
         <v>279</v>
@@ -29432,7 +29432,7 @@
         <v>225</v>
       </c>
       <c r="J27" t="n">
-        <v>225</v>
+        <v>19.1168712588392</v>
       </c>
       <c r="K27" t="n">
         <v>225</v>
@@ -29441,7 +29441,7 @@
         <v>225</v>
       </c>
       <c r="M27" t="n">
-        <v>19.11687125883903</v>
+        <v>225</v>
       </c>
       <c r="N27" t="n">
         <v>225</v>
@@ -29666,13 +29666,13 @@
         <v>251</v>
       </c>
       <c r="I30" t="n">
-        <v>244.1190264315977</v>
+        <v>251</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -29681,16 +29681,16 @@
         <v>251</v>
       </c>
       <c r="N30" t="n">
+        <v>166.1982915220775</v>
+      </c>
+      <c r="O30" t="n">
         <v>251</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
       </c>
       <c r="P30" t="n">
         <v>251</v>
       </c>
       <c r="Q30" t="n">
-        <v>173.0792650904796</v>
+        <v>251</v>
       </c>
       <c r="R30" t="n">
         <v>251</v>
@@ -29903,7 +29903,7 @@
         <v>288</v>
       </c>
       <c r="I33" t="n">
-        <v>217.1263858913485</v>
+        <v>288</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -29918,16 +29918,16 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>278.929543435147</v>
+      </c>
+      <c r="Q33" t="n">
         <v>288</v>
-      </c>
-      <c r="O33" t="n">
-        <v>176.7238924533189</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>173.0792650904796</v>
       </c>
       <c r="R33" t="n">
         <v>288</v>
@@ -30140,7 +30140,7 @@
         <v>288</v>
       </c>
       <c r="I36" t="n">
-        <v>217.1263858913485</v>
+        <v>278.9295434351469</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30155,7 +30155,7 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>176.7238924533192</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -30164,7 +30164,7 @@
         <v>288</v>
       </c>
       <c r="Q36" t="n">
-        <v>173.0792650904796</v>
+        <v>288</v>
       </c>
       <c r="R36" t="n">
         <v>288</v>
@@ -30325,13 +30325,13 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>250.8785988286513</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S38" t="n">
         <v>288</v>
       </c>
       <c r="T38" t="n">
-        <v>288.0000000000126</v>
+        <v>288</v>
       </c>
       <c r="U38" t="n">
         <v>288</v>
@@ -30377,7 +30377,7 @@
         <v>288</v>
       </c>
       <c r="I39" t="n">
-        <v>217.1263858913485</v>
+        <v>278.9295434351469</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30392,16 +30392,16 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
         <v>288</v>
       </c>
-      <c r="O39" t="n">
-        <v>176.7238924533189</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
       <c r="Q39" t="n">
-        <v>173.0792650904796</v>
+        <v>288</v>
       </c>
       <c r="R39" t="n">
         <v>288</v>
@@ -30623,7 +30623,7 @@
         <v>195</v>
       </c>
       <c r="L42" t="n">
-        <v>9.918356100738784</v>
+        <v>195</v>
       </c>
       <c r="M42" t="n">
         <v>195</v>
@@ -30635,7 +30635,7 @@
         <v>195</v>
       </c>
       <c r="P42" t="n">
-        <v>195</v>
+        <v>62.0200712105829</v>
       </c>
       <c r="Q42" t="n">
         <v>195</v>
@@ -30693,10 +30693,10 @@
         <v>195</v>
       </c>
       <c r="I43" t="n">
-        <v>195</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J43" t="n">
-        <v>195</v>
+        <v>77.27857229361456</v>
       </c>
       <c r="K43" t="n">
         <v>195</v>
@@ -30729,7 +30729,7 @@
         <v>195</v>
       </c>
       <c r="U43" t="n">
-        <v>150.9583912744579</v>
+        <v>195</v>
       </c>
       <c r="V43" t="n">
         <v>195</v>
@@ -30854,7 +30854,7 @@
         <v>115</v>
       </c>
       <c r="J45" t="n">
-        <v>115</v>
+        <v>80.77880692081989</v>
       </c>
       <c r="K45" t="n">
         <v>115</v>
@@ -30863,16 +30863,16 @@
         <v>115</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="N45" t="n">
         <v>115</v>
       </c>
       <c r="O45" t="n">
-        <v>56.41509433962264</v>
+        <v>115</v>
       </c>
       <c r="P45" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>115</v>
@@ -30933,7 +30933,7 @@
         <v>115</v>
       </c>
       <c r="J46" t="n">
-        <v>115</v>
+        <v>71.95744110655153</v>
       </c>
       <c r="K46" t="n">
         <v>115</v>
@@ -34749,7 +34749,7 @@
         <v>815</v>
       </c>
       <c r="L2" t="n">
-        <v>783.0093003026099</v>
+        <v>783.0093003026495</v>
       </c>
       <c r="M2" t="n">
         <v>815</v>
@@ -34883,28 +34883,28 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>66.21269765477649</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
         <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>26.66226937777524</v>
       </c>
       <c r="G4" t="n">
         <v>154.95612715847</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J4" t="n">
         <v>364.7310511640923</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34928,22 +34928,22 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -34983,10 +34983,10 @@
         <v>815</v>
       </c>
       <c r="K5" t="n">
+        <v>783.0093003026461</v>
+      </c>
+      <c r="L5" t="n">
         <v>815</v>
-      </c>
-      <c r="L5" t="n">
-        <v>783.0093003026393</v>
       </c>
       <c r="M5" t="n">
         <v>815</v>
@@ -34998,7 +34998,7 @@
         <v>815</v>
       </c>
       <c r="P5" t="n">
-        <v>815</v>
+        <v>815.0000000000011</v>
       </c>
       <c r="Q5" t="n">
         <v>815</v>
@@ -35114,7 +35114,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
         <v>127.2747533519553</v>
@@ -35129,16 +35129,16 @@
         <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I7" t="n">
         <v>223.3665443798817</v>
       </c>
       <c r="J7" t="n">
-        <v>244.5520580454051</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>111.479226198857</v>
@@ -35168,22 +35168,22 @@
         <v>37.62652029714457</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>115.615009061927</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="8">
@@ -35220,7 +35220,7 @@
         <v>815</v>
       </c>
       <c r="K8" t="n">
-        <v>815</v>
+        <v>783.2963603433399</v>
       </c>
       <c r="L8" t="n">
         <v>815</v>
@@ -35232,10 +35232,10 @@
         <v>815</v>
       </c>
       <c r="O8" t="n">
-        <v>783.009300302714</v>
+        <v>815</v>
       </c>
       <c r="P8" t="n">
-        <v>815</v>
+        <v>814.7129399593185</v>
       </c>
       <c r="Q8" t="n">
         <v>815</v>
@@ -35351,13 +35351,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>74.6776987010978</v>
       </c>
       <c r="D10" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -35372,10 +35372,10 @@
         <v>171.2288738983814</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J10" t="n">
-        <v>364.7310511640923</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>111.479226198857</v>
@@ -35402,25 +35402,25 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V10" t="n">
         <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>82.19562742061059</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35454,28 +35454,28 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>395.2617303410664</v>
+        <v>116.7428182785515</v>
       </c>
       <c r="K11" t="n">
-        <v>716.8751175230996</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N11" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O11" t="n">
-        <v>680.5193947875886</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35533,10 +35533,10 @@
         <v>7.873614108651466</v>
       </c>
       <c r="J12" t="n">
-        <v>350.2086062376757</v>
+        <v>144.325477496515</v>
       </c>
       <c r="K12" t="n">
-        <v>210.2207258996306</v>
+        <v>416.1038546407913</v>
       </c>
       <c r="L12" t="n">
         <v>499.091375348687</v>
@@ -35691,25 +35691,25 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>65.19558954760798</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L14" t="n">
-        <v>815</v>
+        <v>559.7722072206399</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O14" t="n">
         <v>815</v>
       </c>
       <c r="P14" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -35773,19 +35773,19 @@
         <v>125.2086062376757</v>
       </c>
       <c r="K15" t="n">
-        <v>470.1038546407913</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L15" t="n">
-        <v>274.091375348687</v>
+        <v>318.5563146339618</v>
       </c>
       <c r="M15" t="n">
         <v>365.9500421645043</v>
       </c>
       <c r="N15" t="n">
-        <v>134.6265501086548</v>
+        <v>413.6265501086548</v>
       </c>
       <c r="O15" t="n">
-        <v>285.9219611880214</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P15" t="n">
         <v>113.6660045146532</v>
@@ -35928,28 +35928,28 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>716.8751175230996</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>814.9999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N17" t="n">
-        <v>484.9338592065413</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O17" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>815</v>
+        <v>116.7428182785516</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36004,10 +36004,10 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>44.46493928527482</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>125.2086062376757</v>
+        <v>404.2086062376757</v>
       </c>
       <c r="K18" t="n">
         <v>470.1038546407913</v>
@@ -36019,13 +36019,13 @@
         <v>86.95004216450428</v>
       </c>
       <c r="N18" t="n">
-        <v>413.6265501086548</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O18" t="n">
         <v>241.4570219027464</v>
       </c>
       <c r="P18" t="n">
-        <v>113.6660045146532</v>
+        <v>158.1309437999284</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -36165,28 +36165,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>716.8751175230994</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L20" t="n">
-        <v>814.9999999999999</v>
+        <v>783.9249412985259</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N20" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
         <v>815</v>
       </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
       <c r="Q20" t="n">
-        <v>260.7811251286549</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36241,10 +36241,10 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>61.87361410865147</v>
       </c>
       <c r="J21" t="n">
-        <v>404.2086062376757</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K21" t="n">
         <v>191.1038546407913</v>
@@ -36253,19 +36253,19 @@
         <v>274.091375348687</v>
       </c>
       <c r="M21" t="n">
-        <v>131.4149814497791</v>
+        <v>242.6206324316071</v>
       </c>
       <c r="N21" t="n">
         <v>134.6265501086548</v>
       </c>
       <c r="O21" t="n">
-        <v>241.4570219027464</v>
+        <v>520.4570219027464</v>
       </c>
       <c r="P21" t="n">
-        <v>392.6660045146532</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>105.9207349095204</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36408,22 +36408,22 @@
         <v>716.8751175230996</v>
       </c>
       <c r="L23" t="n">
-        <v>815</v>
+        <v>164.5104768795734</v>
       </c>
       <c r="M23" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>340.8955523564375</v>
+        <v>815</v>
       </c>
       <c r="Q23" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36478,16 +36478,16 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>61.87361410865147</v>
       </c>
       <c r="J24" t="n">
-        <v>169.6735455229504</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K24" t="n">
         <v>191.1038546407913</v>
       </c>
       <c r="L24" t="n">
-        <v>553.0913753486871</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M24" t="n">
         <v>86.95004216450428</v>
@@ -36496,13 +36496,13 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O24" t="n">
-        <v>241.4570219027464</v>
+        <v>397.1276121698493</v>
       </c>
       <c r="P24" t="n">
         <v>392.6660045146532</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>105.9207349095204</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36642,22 +36642,22 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L26" t="n">
-        <v>774.8401398571921</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N26" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>779.0000000000264</v>
+        <v>677.3794867530461</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>779.0000000000255</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -36718,7 +36718,7 @@
         <v>7.873614108651466</v>
       </c>
       <c r="J27" t="n">
-        <v>350.2086062376757</v>
+        <v>144.3254774965149</v>
       </c>
       <c r="K27" t="n">
         <v>416.1038546407913</v>
@@ -36727,7 +36727,7 @@
         <v>499.091375348687</v>
       </c>
       <c r="M27" t="n">
-        <v>106.0669134233433</v>
+        <v>311.9500421645043</v>
       </c>
       <c r="N27" t="n">
         <v>359.6265501086548</v>
@@ -36879,25 +36879,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
-        <v>688.2341332420267</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>779</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O29" t="n">
-        <v>779.0000000000357</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>779.0000000000357</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>443.0293889420883</v>
+        <v>57.96502233411874</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -36952,13 +36952,13 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>26.9926405402492</v>
+        <v>33.87361410865147</v>
       </c>
       <c r="J30" t="n">
         <v>125.2086062376757</v>
       </c>
       <c r="K30" t="n">
-        <v>442.1038546407913</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L30" t="n">
         <v>274.091375348687</v>
@@ -36967,16 +36967,16 @@
         <v>337.9500421645043</v>
       </c>
       <c r="N30" t="n">
-        <v>385.6265501086548</v>
+        <v>300.8248416307323</v>
       </c>
       <c r="O30" t="n">
-        <v>241.4570219027464</v>
+        <v>492.4570219027464</v>
       </c>
       <c r="P30" t="n">
         <v>364.6660045146532</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>77.92073490952041</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -37113,25 +37113,25 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K32" t="n">
-        <v>764.7137390468165</v>
+        <v>764.713739046811</v>
       </c>
       <c r="L32" t="n">
-        <v>779</v>
+        <v>751.330333511343</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>527.1775994335029</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>779.0000000000457</v>
       </c>
       <c r="Q32" t="n">
         <v>443.0293889420883</v>
@@ -37189,7 +37189,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>70.87361410865147</v>
       </c>
       <c r="J33" t="n">
         <v>125.2086062376757</v>
@@ -37204,16 +37204,16 @@
         <v>86.95004216450428</v>
       </c>
       <c r="N33" t="n">
-        <v>422.6265501086548</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O33" t="n">
-        <v>418.1809143560653</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P33" t="n">
-        <v>113.6660045146532</v>
+        <v>392.5955479498002</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>114.9207349095204</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37353,22 +37353,22 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L35" t="n">
-        <v>779</v>
+        <v>726.1894260691088</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N35" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>560.6589970812406</v>
+        <v>779.0000000000703</v>
       </c>
       <c r="P35" t="n">
-        <v>779.0000000000666</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -37426,7 +37426,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>61.80315754379838</v>
       </c>
       <c r="J36" t="n">
         <v>125.2086062376757</v>
@@ -37441,7 +37441,7 @@
         <v>86.95004216450428</v>
       </c>
       <c r="N36" t="n">
-        <v>311.350442561974</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O36" t="n">
         <v>241.4570219027464</v>
@@ -37450,7 +37450,7 @@
         <v>401.6660045146532</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>114.9207349095204</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37587,31 +37587,31 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>305.467181375627</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K38" t="n">
-        <v>47.83862153580867</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L38" t="n">
-        <v>779</v>
+        <v>442.7455727081267</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O38" t="n">
-        <v>779.0000000000866</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>779.0000000000866</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>443.0293889420883</v>
       </c>
       <c r="R38" t="n">
-        <v>3.569077693321037e-10</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -37663,7 +37663,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>61.80315754379838</v>
       </c>
       <c r="J39" t="n">
         <v>125.2086062376757</v>
@@ -37678,16 +37678,16 @@
         <v>86.95004216450428</v>
       </c>
       <c r="N39" t="n">
-        <v>422.6265501086548</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O39" t="n">
-        <v>418.1809143560653</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P39" t="n">
-        <v>113.6660045146532</v>
+        <v>401.6660045146532</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>114.9207349095204</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37830,7 +37830,7 @@
         <v>716.8751175230996</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>779</v>
       </c>
       <c r="M41" t="n">
         <v>516.0089179080152</v>
@@ -37842,10 +37842,10 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>393.9356333920304</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>443.0293889420883</v>
+        <v>57.96502233411874</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37909,7 +37909,7 @@
         <v>386.1038546407913</v>
       </c>
       <c r="L42" t="n">
-        <v>284.0097314494258</v>
+        <v>469.091375348687</v>
       </c>
       <c r="M42" t="n">
         <v>281.9500421645043</v>
@@ -37921,7 +37921,7 @@
         <v>436.4570219027464</v>
       </c>
       <c r="P42" t="n">
-        <v>308.6660045146532</v>
+        <v>175.6860757252361</v>
       </c>
       <c r="Q42" t="n">
         <v>21.92073490952041</v>
@@ -37979,10 +37979,10 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>18.36654437988173</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>159.7310511640922</v>
+        <v>42.00962345770679</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -38015,7 +38015,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>44.04160872554206</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -38061,25 +38061,25 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>395.2617303410664</v>
+        <v>10.19736373309691</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L44" t="n">
-        <v>172.2252153336802</v>
+        <v>779</v>
       </c>
       <c r="M44" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O44" t="n">
-        <v>779.0000000002012</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>779.0000000002012</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>443.0293889420883</v>
@@ -38140,7 +38140,7 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>240.2086062376757</v>
+        <v>205.9874131584956</v>
       </c>
       <c r="K45" t="n">
         <v>306.1038546407913</v>
@@ -38149,16 +38149,16 @@
         <v>389.091375348687</v>
       </c>
       <c r="M45" t="n">
-        <v>86.95004216450428</v>
+        <v>201.9500421645043</v>
       </c>
       <c r="N45" t="n">
         <v>249.6265501086548</v>
       </c>
       <c r="O45" t="n">
-        <v>297.872116242369</v>
+        <v>356.4570219027464</v>
       </c>
       <c r="P45" t="n">
-        <v>228.6660045146532</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -38219,7 +38219,7 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>79.73105116409224</v>
+        <v>36.68849227064375</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
